--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129319232</v>
       </c>
       <c r="B2" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129319212</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129319211</v>
       </c>
       <c r="B4" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319239</v>
+        <v>129319226</v>
       </c>
       <c r="B5" t="n">
-        <v>80145</v>
+        <v>82990</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541707</v>
+        <v>541943</v>
       </c>
       <c r="R5" t="n">
-        <v>7192111</v>
+        <v>7192145</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319226</v>
+        <v>129319220</v>
       </c>
       <c r="B6" t="n">
-        <v>82988</v>
+        <v>91560</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541943</v>
+        <v>541916</v>
       </c>
       <c r="R6" t="n">
-        <v>7192145</v>
+        <v>7192172</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319220</v>
+        <v>129319239</v>
       </c>
       <c r="B7" t="n">
-        <v>91558</v>
+        <v>80147</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541916</v>
+        <v>541707</v>
       </c>
       <c r="R7" t="n">
-        <v>7192172</v>
+        <v>7192111</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,7 +1320,7 @@
         <v>129319222</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129319218</v>
+        <v>129319229</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>91827</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541948</v>
+        <v>541938</v>
       </c>
       <c r="R9" t="n">
-        <v>7192187</v>
+        <v>7192121</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129319229</v>
+        <v>129319218</v>
       </c>
       <c r="B10" t="n">
-        <v>91825</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541938</v>
+        <v>541948</v>
       </c>
       <c r="R10" t="n">
-        <v>7192121</v>
+        <v>7192187</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,7 +1641,7 @@
         <v>129319224</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319240</v>
+        <v>129319215</v>
       </c>
       <c r="B12" t="n">
-        <v>80145</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541698</v>
+        <v>541988</v>
       </c>
       <c r="R12" t="n">
-        <v>7192119</v>
+        <v>7192224</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,7 +1855,7 @@
         <v>129319242</v>
       </c>
       <c r="B13" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,10 +1963,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129319215</v>
+        <v>129319240</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>80147</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1974,21 +1974,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541988</v>
+        <v>541698</v>
       </c>
       <c r="R14" t="n">
-        <v>7192224</v>
+        <v>7192119</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2073,7 +2073,7 @@
         <v>129319238</v>
       </c>
       <c r="B15" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>129319221</v>
       </c>
       <c r="B16" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>129319237</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>129319246</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>129319219</v>
       </c>
       <c r="B19" t="n">
-        <v>82871</v>
+        <v>82873</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>129319228</v>
       </c>
       <c r="B20" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>129319214</v>
       </c>
       <c r="B21" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>129319216</v>
       </c>
       <c r="B22" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>129319231</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319225</v>
+        <v>129319244</v>
       </c>
       <c r="B24" t="n">
-        <v>82871</v>
+        <v>80147</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541939</v>
+        <v>541664</v>
       </c>
       <c r="R24" t="n">
-        <v>7192143</v>
+        <v>7192124</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3140,32 +3140,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129319230</v>
+        <v>129319223</v>
       </c>
       <c r="B25" t="n">
-        <v>91540</v>
+        <v>92242</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3175,10 +3175,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541937</v>
+        <v>541931</v>
       </c>
       <c r="R25" t="n">
-        <v>7192124</v>
+        <v>7192153</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3247,32 +3247,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319244</v>
+        <v>129319213</v>
       </c>
       <c r="B26" t="n">
-        <v>80145</v>
+        <v>92480</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>4769</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541664</v>
+        <v>541932</v>
       </c>
       <c r="R26" t="n">
-        <v>7192124</v>
+        <v>7192500</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3354,32 +3354,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319223</v>
+        <v>129319230</v>
       </c>
       <c r="B27" t="n">
-        <v>92240</v>
+        <v>91542</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541931</v>
+        <v>541937</v>
       </c>
       <c r="R27" t="n">
-        <v>7192153</v>
+        <v>7192124</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3461,32 +3461,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319213</v>
+        <v>129319225</v>
       </c>
       <c r="B28" t="n">
-        <v>92478</v>
+        <v>82873</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4769</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541932</v>
+        <v>541939</v>
       </c>
       <c r="R28" t="n">
-        <v>7192500</v>
+        <v>7192143</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3571,7 +3571,7 @@
         <v>129319235</v>
       </c>
       <c r="B29" t="n">
-        <v>95902</v>
+        <v>95904</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319236</v>
+        <v>129319234</v>
       </c>
       <c r="B30" t="n">
-        <v>80145</v>
+        <v>91542</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3686,21 +3686,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541880</v>
+        <v>541913</v>
       </c>
       <c r="R30" t="n">
-        <v>7192165</v>
+        <v>7192150</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3785,7 +3785,7 @@
         <v>129319233</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>129319227</v>
       </c>
       <c r="B32" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,10 +3996,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319234</v>
+        <v>129319236</v>
       </c>
       <c r="B33" t="n">
-        <v>91540</v>
+        <v>80147</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,21 +4007,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541913</v>
+        <v>541880</v>
       </c>
       <c r="R33" t="n">
-        <v>7192150</v>
+        <v>7192165</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129319212</v>
+        <v>129319211</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541941</v>
+        <v>541952</v>
       </c>
       <c r="R3" t="n">
-        <v>7192545</v>
+        <v>7192657</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129319211</v>
+        <v>129319212</v>
       </c>
       <c r="B4" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541952</v>
+        <v>541941</v>
       </c>
       <c r="R4" t="n">
-        <v>7192657</v>
+        <v>7192545</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319226</v>
+        <v>129319239</v>
       </c>
       <c r="B5" t="n">
-        <v>82990</v>
+        <v>80147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541943</v>
+        <v>541707</v>
       </c>
       <c r="R5" t="n">
-        <v>7192145</v>
+        <v>7192111</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,32 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319239</v>
+        <v>129319226</v>
       </c>
       <c r="B7" t="n">
-        <v>80147</v>
+        <v>82990</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541707</v>
+        <v>541943</v>
       </c>
       <c r="R7" t="n">
-        <v>7192111</v>
+        <v>7192145</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319215</v>
+        <v>129319240</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541988</v>
+        <v>541698</v>
       </c>
       <c r="R12" t="n">
-        <v>7192224</v>
+        <v>7192119</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129319242</v>
+        <v>129319215</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,38 +1863,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541676</v>
+        <v>541988</v>
       </c>
       <c r="R13" t="n">
-        <v>7192124</v>
+        <v>7192224</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1926,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1936,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1963,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129319240</v>
+        <v>129319242</v>
       </c>
       <c r="B14" t="n">
-        <v>80147</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1974,34 +1970,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541698</v>
+        <v>541676</v>
       </c>
       <c r="R14" t="n">
-        <v>7192119</v>
+        <v>7192124</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2926,10 +2926,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319231</v>
+        <v>129319230</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2937,21 +2937,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319244</v>
+        <v>129319225</v>
       </c>
       <c r="B24" t="n">
-        <v>80147</v>
+        <v>82873</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541664</v>
+        <v>541939</v>
       </c>
       <c r="R24" t="n">
-        <v>7192124</v>
+        <v>7192143</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3140,32 +3140,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129319223</v>
+        <v>129319244</v>
       </c>
       <c r="B25" t="n">
-        <v>92242</v>
+        <v>80147</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3175,10 +3175,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541931</v>
+        <v>541664</v>
       </c>
       <c r="R25" t="n">
-        <v>7192153</v>
+        <v>7192124</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3247,10 +3247,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319213</v>
+        <v>129319223</v>
       </c>
       <c r="B26" t="n">
-        <v>92480</v>
+        <v>92242</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3258,21 +3258,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541932</v>
+        <v>541931</v>
       </c>
       <c r="R26" t="n">
-        <v>7192500</v>
+        <v>7192153</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3354,32 +3354,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319230</v>
+        <v>129319213</v>
       </c>
       <c r="B27" t="n">
-        <v>91542</v>
+        <v>92480</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541937</v>
+        <v>541932</v>
       </c>
       <c r="R27" t="n">
-        <v>7192124</v>
+        <v>7192500</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3461,10 +3461,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319225</v>
+        <v>129319231</v>
       </c>
       <c r="B28" t="n">
-        <v>82873</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3472,21 +3472,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541939</v>
+        <v>541937</v>
       </c>
       <c r="R28" t="n">
-        <v>7192143</v>
+        <v>7192124</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3675,10 +3675,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319234</v>
+        <v>129319233</v>
       </c>
       <c r="B30" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3686,21 +3686,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541913</v>
+        <v>541922</v>
       </c>
       <c r="R30" t="n">
-        <v>7192150</v>
+        <v>7192128</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3782,7 +3782,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129319233</v>
+        <v>129319227</v>
       </c>
       <c r="B31" t="n">
         <v>79041</v>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541922</v>
+        <v>541943</v>
       </c>
       <c r="R31" t="n">
-        <v>7192128</v>
+        <v>7192145</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3889,10 +3889,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129319227</v>
+        <v>129319236</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3900,21 +3900,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541943</v>
+        <v>541880</v>
       </c>
       <c r="R32" t="n">
-        <v>7192145</v>
+        <v>7192165</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3996,10 +3996,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319236</v>
+        <v>129319234</v>
       </c>
       <c r="B33" t="n">
-        <v>80147</v>
+        <v>91542</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,21 +4007,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541880</v>
+        <v>541913</v>
       </c>
       <c r="R33" t="n">
-        <v>7192165</v>
+        <v>7192150</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -2926,32 +2926,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319230</v>
+        <v>129319223</v>
       </c>
       <c r="B23" t="n">
-        <v>91542</v>
+        <v>92242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541937</v>
+        <v>541931</v>
       </c>
       <c r="R23" t="n">
-        <v>7192124</v>
+        <v>7192153</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3033,32 +3033,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319225</v>
+        <v>129319213</v>
       </c>
       <c r="B24" t="n">
-        <v>82873</v>
+        <v>92480</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541939</v>
+        <v>541932</v>
       </c>
       <c r="R24" t="n">
-        <v>7192143</v>
+        <v>7192500</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3140,10 +3140,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129319244</v>
+        <v>129319231</v>
       </c>
       <c r="B25" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3151,21 +3151,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541664</v>
+        <v>541937</v>
       </c>
       <c r="R25" t="n">
         <v>7192124</v>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3247,32 +3247,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319223</v>
+        <v>129319230</v>
       </c>
       <c r="B26" t="n">
-        <v>92242</v>
+        <v>91542</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541931</v>
+        <v>541937</v>
       </c>
       <c r="R26" t="n">
-        <v>7192153</v>
+        <v>7192124</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3354,32 +3354,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319213</v>
+        <v>129319225</v>
       </c>
       <c r="B27" t="n">
-        <v>92480</v>
+        <v>82873</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4769</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541932</v>
+        <v>541939</v>
       </c>
       <c r="R27" t="n">
-        <v>7192500</v>
+        <v>7192143</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3461,10 +3461,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319231</v>
+        <v>129319244</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3472,21 +3472,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541937</v>
+        <v>541664</v>
       </c>
       <c r="R28" t="n">
         <v>7192124</v>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129319232</v>
       </c>
       <c r="B2" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1103,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319220</v>
+        <v>129319226</v>
       </c>
       <c r="B6" t="n">
-        <v>91560</v>
+        <v>82990</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541916</v>
+        <v>541943</v>
       </c>
       <c r="R6" t="n">
-        <v>7192172</v>
+        <v>7192145</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,32 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319226</v>
+        <v>129319220</v>
       </c>
       <c r="B7" t="n">
-        <v>82990</v>
+        <v>91558</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541943</v>
+        <v>541916</v>
       </c>
       <c r="R7" t="n">
-        <v>7192145</v>
+        <v>7192172</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,7 +1427,7 @@
         <v>129319229</v>
       </c>
       <c r="B9" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319240</v>
+        <v>129319215</v>
       </c>
       <c r="B12" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541698</v>
+        <v>541988</v>
       </c>
       <c r="R12" t="n">
-        <v>7192119</v>
+        <v>7192224</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129319215</v>
+        <v>129319240</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541988</v>
+        <v>541698</v>
       </c>
       <c r="R13" t="n">
-        <v>7192224</v>
+        <v>7192119</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2180,7 +2180,7 @@
         <v>129319221</v>
       </c>
       <c r="B16" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2391,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129319246</v>
+        <v>129319219</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>82873</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,21 +2402,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541653</v>
+        <v>541925</v>
       </c>
       <c r="R18" t="n">
-        <v>7192124</v>
+        <v>7192171</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2498,10 +2498,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129319219</v>
+        <v>129319246</v>
       </c>
       <c r="B19" t="n">
-        <v>82873</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,21 +2509,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541925</v>
+        <v>541653</v>
       </c>
       <c r="R19" t="n">
-        <v>7192171</v>
+        <v>7192124</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2605,10 +2605,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129319228</v>
+        <v>129319214</v>
       </c>
       <c r="B20" t="n">
-        <v>91560</v>
+        <v>80146</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2616,21 +2616,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541949</v>
+        <v>541967</v>
       </c>
       <c r="R20" t="n">
-        <v>7192127</v>
+        <v>7192412</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2712,10 +2712,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129319214</v>
+        <v>129319228</v>
       </c>
       <c r="B21" t="n">
-        <v>80146</v>
+        <v>91558</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,21 +2723,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541967</v>
+        <v>541949</v>
       </c>
       <c r="R21" t="n">
-        <v>7192412</v>
+        <v>7192127</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2822,7 +2822,7 @@
         <v>129319216</v>
       </c>
       <c r="B22" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,32 +2926,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319223</v>
+        <v>129319225</v>
       </c>
       <c r="B23" t="n">
-        <v>92242</v>
+        <v>82873</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541931</v>
+        <v>541939</v>
       </c>
       <c r="R23" t="n">
-        <v>7192153</v>
+        <v>7192143</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3033,32 +3033,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319213</v>
+        <v>129319244</v>
       </c>
       <c r="B24" t="n">
-        <v>92480</v>
+        <v>80147</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4769</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541932</v>
+        <v>541664</v>
       </c>
       <c r="R24" t="n">
-        <v>7192500</v>
+        <v>7192124</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3140,10 +3140,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129319231</v>
+        <v>129319230</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3151,21 +3151,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3247,32 +3247,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319230</v>
+        <v>129319223</v>
       </c>
       <c r="B26" t="n">
-        <v>91542</v>
+        <v>92257</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541937</v>
+        <v>541931</v>
       </c>
       <c r="R26" t="n">
-        <v>7192124</v>
+        <v>7192153</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3354,10 +3354,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319225</v>
+        <v>129319231</v>
       </c>
       <c r="B27" t="n">
-        <v>82873</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3365,21 +3365,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541939</v>
+        <v>541937</v>
       </c>
       <c r="R27" t="n">
-        <v>7192143</v>
+        <v>7192124</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3461,32 +3461,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319244</v>
+        <v>129319213</v>
       </c>
       <c r="B28" t="n">
-        <v>80147</v>
+        <v>92494</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541664</v>
+        <v>541932</v>
       </c>
       <c r="R28" t="n">
-        <v>7192124</v>
+        <v>7192500</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3571,7 +3571,7 @@
         <v>129319235</v>
       </c>
       <c r="B29" t="n">
-        <v>95904</v>
+        <v>95930</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3675,10 +3675,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319233</v>
+        <v>129319236</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3686,21 +3686,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541922</v>
+        <v>541880</v>
       </c>
       <c r="R30" t="n">
-        <v>7192128</v>
+        <v>7192165</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3782,10 +3782,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129319227</v>
+        <v>129319234</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3793,21 +3793,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541943</v>
+        <v>541913</v>
       </c>
       <c r="R31" t="n">
-        <v>7192145</v>
+        <v>7192150</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3889,10 +3889,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129319236</v>
+        <v>129319233</v>
       </c>
       <c r="B32" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3900,21 +3900,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541880</v>
+        <v>541922</v>
       </c>
       <c r="R32" t="n">
-        <v>7192165</v>
+        <v>7192128</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3996,10 +3996,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319234</v>
+        <v>129319227</v>
       </c>
       <c r="B33" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4007,21 +4007,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541913</v>
+        <v>541943</v>
       </c>
       <c r="R33" t="n">
-        <v>7192150</v>
+        <v>7192145</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129319232</v>
       </c>
       <c r="B2" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1103,34 +1103,30 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319226</v>
+        <v>129319220</v>
       </c>
       <c r="B6" t="n">
-        <v>82990</v>
+        <v>91560</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1138,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541943</v>
+        <v>541916</v>
       </c>
       <c r="R6" t="n">
-        <v>7192145</v>
+        <v>7192172</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1173,7 +1169,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1179,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,32 +1206,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319220</v>
+        <v>129319226</v>
       </c>
       <c r="B7" t="n">
-        <v>91558</v>
+        <v>82990</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541916</v>
+        <v>541943</v>
       </c>
       <c r="R7" t="n">
-        <v>7192172</v>
+        <v>7192145</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1280,7 +1276,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,7 +1423,7 @@
         <v>129319229</v>
       </c>
       <c r="B9" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1745,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319215</v>
+        <v>129319242</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,34 +1752,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541988</v>
+        <v>541676</v>
       </c>
       <c r="R12" t="n">
-        <v>7192224</v>
+        <v>7192124</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129319240</v>
+        <v>129319215</v>
       </c>
       <c r="B13" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541698</v>
+        <v>541988</v>
       </c>
       <c r="R13" t="n">
-        <v>7192119</v>
+        <v>7192224</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129319242</v>
+        <v>129319240</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>80147</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,38 +1970,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541676</v>
+        <v>541698</v>
       </c>
       <c r="R14" t="n">
-        <v>7192124</v>
+        <v>7192119</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2033,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2043,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2180,7 +2176,7 @@
         <v>129319221</v>
       </c>
       <c r="B16" t="n">
-        <v>97575</v>
+        <v>97576</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2605,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129319214</v>
+        <v>129319228</v>
       </c>
       <c r="B20" t="n">
-        <v>80146</v>
+        <v>91560</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2616,23 +2612,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2640,10 +2632,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541967</v>
+        <v>541949</v>
       </c>
       <c r="R20" t="n">
-        <v>7192412</v>
+        <v>7192127</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2675,7 +2667,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2685,7 +2677,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2712,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129319228</v>
+        <v>129319214</v>
       </c>
       <c r="B21" t="n">
-        <v>91558</v>
+        <v>80146</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,21 +2715,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2747,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541949</v>
+        <v>541967</v>
       </c>
       <c r="R21" t="n">
-        <v>7192127</v>
+        <v>7192412</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2782,7 +2774,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2792,7 +2784,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2822,7 +2814,7 @@
         <v>129319216</v>
       </c>
       <c r="B22" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2839,14 +2831,10 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2926,10 +2914,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319225</v>
+        <v>129319244</v>
       </c>
       <c r="B23" t="n">
-        <v>82873</v>
+        <v>80147</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2937,21 +2925,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2961,10 +2949,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541939</v>
+        <v>541664</v>
       </c>
       <c r="R23" t="n">
-        <v>7192143</v>
+        <v>7192124</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2996,7 +2984,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3006,7 +2994,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3033,32 +3021,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319244</v>
+        <v>129319223</v>
       </c>
       <c r="B24" t="n">
-        <v>80147</v>
+        <v>92258</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3068,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541664</v>
+        <v>541931</v>
       </c>
       <c r="R24" t="n">
-        <v>7192124</v>
+        <v>7192153</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3103,7 +3091,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3113,7 +3101,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3247,32 +3235,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319223</v>
+        <v>129319225</v>
       </c>
       <c r="B26" t="n">
-        <v>92257</v>
+        <v>82873</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3282,10 +3270,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541931</v>
+        <v>541939</v>
       </c>
       <c r="R26" t="n">
-        <v>7192153</v>
+        <v>7192143</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3317,7 +3305,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3327,7 +3315,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3464,7 +3452,7 @@
         <v>129319213</v>
       </c>
       <c r="B28" t="n">
-        <v>92494</v>
+        <v>92495</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3571,7 +3559,7 @@
         <v>129319235</v>
       </c>
       <c r="B29" t="n">
-        <v>95930</v>
+        <v>95931</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3889,7 +3877,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129319233</v>
+        <v>129319227</v>
       </c>
       <c r="B32" t="n">
         <v>79041</v>
@@ -3924,10 +3912,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541922</v>
+        <v>541943</v>
       </c>
       <c r="R32" t="n">
-        <v>7192128</v>
+        <v>7192145</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3959,7 +3947,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3969,7 +3957,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3996,7 +3984,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319227</v>
+        <v>129319233</v>
       </c>
       <c r="B33" t="n">
         <v>79041</v>
@@ -4031,10 +4019,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541943</v>
+        <v>541922</v>
       </c>
       <c r="R33" t="n">
-        <v>7192145</v>
+        <v>7192128</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4066,7 +4054,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4076,7 +4064,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319242</v>
+        <v>129319240</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>80147</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,38 +1752,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541676</v>
+        <v>541698</v>
       </c>
       <c r="R12" t="n">
-        <v>7192124</v>
+        <v>7192119</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1815,7 +1811,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1821,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129319240</v>
+        <v>129319242</v>
       </c>
       <c r="B14" t="n">
-        <v>80147</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,34 +1966,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541698</v>
+        <v>541676</v>
       </c>
       <c r="R14" t="n">
-        <v>7192119</v>
+        <v>7192124</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,7 +2176,7 @@
         <v>129319221</v>
       </c>
       <c r="B16" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129319228</v>
+        <v>129319214</v>
       </c>
       <c r="B20" t="n">
-        <v>91560</v>
+        <v>80146</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,19 +2612,23 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2632,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541949</v>
+        <v>541967</v>
       </c>
       <c r="R20" t="n">
-        <v>7192127</v>
+        <v>7192412</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2667,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2677,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129319214</v>
+        <v>129319228</v>
       </c>
       <c r="B21" t="n">
-        <v>80146</v>
+        <v>91560</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2715,23 +2719,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541967</v>
+        <v>541949</v>
       </c>
       <c r="R21" t="n">
-        <v>7192412</v>
+        <v>7192127</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2914,10 +2914,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319244</v>
+        <v>129319231</v>
       </c>
       <c r="B23" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2925,21 +2925,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541664</v>
+        <v>541937</v>
       </c>
       <c r="R23" t="n">
         <v>7192124</v>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3021,32 +3021,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319223</v>
+        <v>129319225</v>
       </c>
       <c r="B24" t="n">
-        <v>92258</v>
+        <v>82873</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541931</v>
+        <v>541939</v>
       </c>
       <c r="R24" t="n">
-        <v>7192153</v>
+        <v>7192143</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3128,10 +3128,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129319230</v>
+        <v>129319244</v>
       </c>
       <c r="B25" t="n">
-        <v>91540</v>
+        <v>80147</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541937</v>
+        <v>541664</v>
       </c>
       <c r="R25" t="n">
         <v>7192124</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,10 +3235,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319225</v>
+        <v>129319230</v>
       </c>
       <c r="B26" t="n">
-        <v>82873</v>
+        <v>91540</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3246,21 +3246,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541939</v>
+        <v>541937</v>
       </c>
       <c r="R26" t="n">
-        <v>7192143</v>
+        <v>7192124</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3342,32 +3342,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319231</v>
+        <v>129319223</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>92258</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541937</v>
+        <v>541931</v>
       </c>
       <c r="R27" t="n">
-        <v>7192124</v>
+        <v>7192153</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3559,7 +3559,7 @@
         <v>129319235</v>
       </c>
       <c r="B29" t="n">
-        <v>95931</v>
+        <v>95932</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3663,10 +3663,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319236</v>
+        <v>129319233</v>
       </c>
       <c r="B30" t="n">
-        <v>80147</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3674,21 +3674,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541880</v>
+        <v>541922</v>
       </c>
       <c r="R30" t="n">
-        <v>7192165</v>
+        <v>7192128</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3770,10 +3770,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129319234</v>
+        <v>129319227</v>
       </c>
       <c r="B31" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3781,21 +3781,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541913</v>
+        <v>541943</v>
       </c>
       <c r="R31" t="n">
-        <v>7192150</v>
+        <v>7192145</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3877,10 +3877,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129319227</v>
+        <v>129319236</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>80147</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,21 +3888,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541943</v>
+        <v>541880</v>
       </c>
       <c r="R32" t="n">
-        <v>7192145</v>
+        <v>7192165</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3984,10 +3984,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319233</v>
+        <v>129319234</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,21 +3995,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541922</v>
+        <v>541913</v>
       </c>
       <c r="R33" t="n">
-        <v>7192128</v>
+        <v>7192150</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129319232</v>
       </c>
       <c r="B2" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129319211</v>
       </c>
       <c r="B3" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129319212</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319239</v>
+        <v>129319226</v>
       </c>
       <c r="B5" t="n">
-        <v>80147</v>
+        <v>82994</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541707</v>
+        <v>541943</v>
       </c>
       <c r="R5" t="n">
-        <v>7192111</v>
+        <v>7192145</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319220</v>
+        <v>129319239</v>
       </c>
       <c r="B6" t="n">
-        <v>91560</v>
+        <v>80149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,19 +1114,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1134,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541916</v>
+        <v>541707</v>
       </c>
       <c r="R6" t="n">
-        <v>7192172</v>
+        <v>7192111</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1169,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1179,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,34 +1210,30 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319226</v>
+        <v>129319220</v>
       </c>
       <c r="B7" t="n">
-        <v>82990</v>
+        <v>91563</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541943</v>
+        <v>541916</v>
       </c>
       <c r="R7" t="n">
-        <v>7192145</v>
+        <v>7192172</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,7 +1316,7 @@
         <v>129319222</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>129319229</v>
       </c>
       <c r="B9" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129319218</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>129319224</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319240</v>
+        <v>129319215</v>
       </c>
       <c r="B12" t="n">
-        <v>80147</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,21 +1752,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541698</v>
+        <v>541988</v>
       </c>
       <c r="R12" t="n">
-        <v>7192119</v>
+        <v>7192224</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,10 +1848,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129319215</v>
+        <v>129319240</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541988</v>
+        <v>541698</v>
       </c>
       <c r="R13" t="n">
-        <v>7192224</v>
+        <v>7192119</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2069,7 +2069,7 @@
         <v>129319238</v>
       </c>
       <c r="B15" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>129319221</v>
       </c>
       <c r="B16" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>129319237</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129319219</v>
       </c>
       <c r="B18" t="n">
-        <v>82873</v>
+        <v>82877</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>129319246</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129319214</v>
+        <v>129319228</v>
       </c>
       <c r="B20" t="n">
-        <v>80146</v>
+        <v>91563</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,23 +2612,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2636,10 +2632,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541967</v>
+        <v>541949</v>
       </c>
       <c r="R20" t="n">
-        <v>7192412</v>
+        <v>7192127</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2671,7 +2667,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2677,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129319228</v>
+        <v>129319214</v>
       </c>
       <c r="B21" t="n">
-        <v>91560</v>
+        <v>80148</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,19 +2715,23 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541949</v>
+        <v>541967</v>
       </c>
       <c r="R21" t="n">
-        <v>7192127</v>
+        <v>7192412</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2814,7 +2814,7 @@
         <v>129319216</v>
       </c>
       <c r="B22" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,10 +2914,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319231</v>
+        <v>129319230</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>91543</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2925,21 +2925,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3024,7 +3024,7 @@
         <v>129319225</v>
       </c>
       <c r="B24" t="n">
-        <v>82873</v>
+        <v>82877</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>129319244</v>
       </c>
       <c r="B25" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319230</v>
+        <v>129319231</v>
       </c>
       <c r="B26" t="n">
-        <v>91540</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3246,21 +3246,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3345,7 +3345,7 @@
         <v>129319223</v>
       </c>
       <c r="B27" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>129319213</v>
       </c>
       <c r="B28" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>129319235</v>
       </c>
       <c r="B29" t="n">
-        <v>95932</v>
+        <v>95936</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3663,10 +3663,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319233</v>
+        <v>129319234</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>91543</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3674,21 +3674,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541922</v>
+        <v>541913</v>
       </c>
       <c r="R30" t="n">
-        <v>7192128</v>
+        <v>7192150</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3770,10 +3770,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129319227</v>
+        <v>129319236</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>80149</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3781,21 +3781,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541943</v>
+        <v>541880</v>
       </c>
       <c r="R31" t="n">
-        <v>7192145</v>
+        <v>7192165</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3877,10 +3877,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129319236</v>
+        <v>129319227</v>
       </c>
       <c r="B32" t="n">
-        <v>80147</v>
+        <v>79043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,21 +3888,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541880</v>
+        <v>541943</v>
       </c>
       <c r="R32" t="n">
-        <v>7192165</v>
+        <v>7192145</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3984,10 +3984,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319234</v>
+        <v>129319233</v>
       </c>
       <c r="B33" t="n">
-        <v>91540</v>
+        <v>79043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,21 +3995,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541913</v>
+        <v>541922</v>
       </c>
       <c r="R33" t="n">
-        <v>7192150</v>
+        <v>7192128</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319226</v>
+        <v>129319239</v>
       </c>
       <c r="B5" t="n">
-        <v>82994</v>
+        <v>80149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541943</v>
+        <v>541707</v>
       </c>
       <c r="R5" t="n">
-        <v>7192145</v>
+        <v>7192111</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319239</v>
+        <v>129319220</v>
       </c>
       <c r="B6" t="n">
-        <v>80149</v>
+        <v>91563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,23 +1114,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1138,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541707</v>
+        <v>541916</v>
       </c>
       <c r="R6" t="n">
-        <v>7192111</v>
+        <v>7192172</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1173,7 +1169,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1179,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,30 +1206,34 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319220</v>
+        <v>129319226</v>
       </c>
       <c r="B7" t="n">
-        <v>91563</v>
+        <v>82994</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541916</v>
+        <v>541943</v>
       </c>
       <c r="R7" t="n">
-        <v>7192172</v>
+        <v>7192145</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129319229</v>
+        <v>129319218</v>
       </c>
       <c r="B9" t="n">
-        <v>91841</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1431,21 +1431,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541938</v>
+        <v>541948</v>
       </c>
       <c r="R9" t="n">
-        <v>7192121</v>
+        <v>7192187</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129319218</v>
+        <v>129319229</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>91841</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1538,21 +1538,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541948</v>
+        <v>541938</v>
       </c>
       <c r="R10" t="n">
-        <v>7192187</v>
+        <v>7192121</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129319228</v>
+        <v>129319214</v>
       </c>
       <c r="B20" t="n">
-        <v>91563</v>
+        <v>80148</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,19 +2612,23 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2632,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541949</v>
+        <v>541967</v>
       </c>
       <c r="R20" t="n">
-        <v>7192127</v>
+        <v>7192412</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2667,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2677,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129319214</v>
+        <v>129319228</v>
       </c>
       <c r="B21" t="n">
-        <v>80148</v>
+        <v>91563</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2715,23 +2719,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541967</v>
+        <v>541949</v>
       </c>
       <c r="R21" t="n">
-        <v>7192412</v>
+        <v>7192127</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3021,10 +3021,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319225</v>
+        <v>129319231</v>
       </c>
       <c r="B24" t="n">
-        <v>82877</v>
+        <v>79043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3032,21 +3032,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541939</v>
+        <v>541937</v>
       </c>
       <c r="R24" t="n">
-        <v>7192143</v>
+        <v>7192124</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3128,32 +3128,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129319244</v>
+        <v>129319213</v>
       </c>
       <c r="B25" t="n">
-        <v>80149</v>
+        <v>92498</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>4769</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541664</v>
+        <v>541932</v>
       </c>
       <c r="R25" t="n">
-        <v>7192124</v>
+        <v>7192500</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,32 +3235,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319231</v>
+        <v>129319223</v>
       </c>
       <c r="B26" t="n">
-        <v>79043</v>
+        <v>92261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541937</v>
+        <v>541931</v>
       </c>
       <c r="R26" t="n">
-        <v>7192124</v>
+        <v>7192153</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3342,32 +3342,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319223</v>
+        <v>129319225</v>
       </c>
       <c r="B27" t="n">
-        <v>92261</v>
+        <v>82877</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541931</v>
+        <v>541939</v>
       </c>
       <c r="R27" t="n">
-        <v>7192153</v>
+        <v>7192143</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3449,32 +3449,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319213</v>
+        <v>129319244</v>
       </c>
       <c r="B28" t="n">
-        <v>92498</v>
+        <v>80149</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4769</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541932</v>
+        <v>541664</v>
       </c>
       <c r="R28" t="n">
-        <v>7192500</v>
+        <v>7192124</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3663,10 +3663,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319234</v>
+        <v>129319236</v>
       </c>
       <c r="B30" t="n">
-        <v>91543</v>
+        <v>80149</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3674,21 +3674,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541913</v>
+        <v>541880</v>
       </c>
       <c r="R30" t="n">
-        <v>7192150</v>
+        <v>7192165</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3770,10 +3770,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129319236</v>
+        <v>129319227</v>
       </c>
       <c r="B31" t="n">
-        <v>80149</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3781,21 +3781,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541880</v>
+        <v>541943</v>
       </c>
       <c r="R31" t="n">
-        <v>7192165</v>
+        <v>7192145</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3877,7 +3877,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129319227</v>
+        <v>129319233</v>
       </c>
       <c r="B32" t="n">
         <v>79043</v>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541943</v>
+        <v>541922</v>
       </c>
       <c r="R32" t="n">
-        <v>7192145</v>
+        <v>7192128</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3984,10 +3984,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319233</v>
+        <v>129319234</v>
       </c>
       <c r="B33" t="n">
-        <v>79043</v>
+        <v>91543</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,21 +3995,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541922</v>
+        <v>541913</v>
       </c>
       <c r="R33" t="n">
-        <v>7192128</v>
+        <v>7192150</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129319232</v>
       </c>
       <c r="B2" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129319211</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129319212</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319239</v>
+        <v>129319220</v>
       </c>
       <c r="B5" t="n">
-        <v>80149</v>
+        <v>91565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,23 +1007,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1031,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541707</v>
+        <v>541916</v>
       </c>
       <c r="R5" t="n">
-        <v>7192111</v>
+        <v>7192172</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,7 +1062,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1072,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319220</v>
+        <v>129319239</v>
       </c>
       <c r="B6" t="n">
-        <v>91563</v>
+        <v>80150</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,19 +1110,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541916</v>
+        <v>541707</v>
       </c>
       <c r="R6" t="n">
-        <v>7192172</v>
+        <v>7192111</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,7 +1209,7 @@
         <v>129319226</v>
       </c>
       <c r="B7" t="n">
-        <v>82994</v>
+        <v>82995</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>129319222</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129319218</v>
+        <v>129319229</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>91843</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1431,21 +1431,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541948</v>
+        <v>541938</v>
       </c>
       <c r="R9" t="n">
-        <v>7192187</v>
+        <v>7192121</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129319229</v>
+        <v>129319218</v>
       </c>
       <c r="B10" t="n">
-        <v>91841</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1538,21 +1538,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541938</v>
+        <v>541948</v>
       </c>
       <c r="R10" t="n">
-        <v>7192121</v>
+        <v>7192187</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1637,7 +1637,7 @@
         <v>129319224</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319215</v>
+        <v>129319240</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>80150</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,21 +1752,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541988</v>
+        <v>541698</v>
       </c>
       <c r="R12" t="n">
-        <v>7192224</v>
+        <v>7192119</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,10 +1848,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129319240</v>
+        <v>129319215</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541698</v>
+        <v>541988</v>
       </c>
       <c r="R13" t="n">
-        <v>7192119</v>
+        <v>7192224</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2069,7 +2069,7 @@
         <v>129319238</v>
       </c>
       <c r="B15" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>129319221</v>
       </c>
       <c r="B16" t="n">
-        <v>97581</v>
+        <v>97583</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>129319237</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129319219</v>
       </c>
       <c r="B18" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>129319246</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129319214</v>
+        <v>129319228</v>
       </c>
       <c r="B20" t="n">
-        <v>80148</v>
+        <v>91565</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,23 +2612,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2636,10 +2632,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541967</v>
+        <v>541949</v>
       </c>
       <c r="R20" t="n">
-        <v>7192412</v>
+        <v>7192127</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2671,7 +2667,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2677,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129319228</v>
+        <v>129319214</v>
       </c>
       <c r="B21" t="n">
-        <v>91563</v>
+        <v>80149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,19 +2715,23 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541949</v>
+        <v>541967</v>
       </c>
       <c r="R21" t="n">
-        <v>7192127</v>
+        <v>7192412</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2814,7 +2814,7 @@
         <v>129319216</v>
       </c>
       <c r="B22" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,32 +2914,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319230</v>
+        <v>129319223</v>
       </c>
       <c r="B23" t="n">
-        <v>91543</v>
+        <v>92263</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541937</v>
+        <v>541931</v>
       </c>
       <c r="R23" t="n">
-        <v>7192124</v>
+        <v>7192153</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3021,32 +3021,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319231</v>
+        <v>129319213</v>
       </c>
       <c r="B24" t="n">
-        <v>79043</v>
+        <v>92500</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541937</v>
+        <v>541932</v>
       </c>
       <c r="R24" t="n">
-        <v>7192124</v>
+        <v>7192500</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3128,32 +3128,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129319213</v>
+        <v>129319231</v>
       </c>
       <c r="B25" t="n">
-        <v>92498</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541932</v>
+        <v>541937</v>
       </c>
       <c r="R25" t="n">
-        <v>7192500</v>
+        <v>7192124</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,32 +3235,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319223</v>
+        <v>129319230</v>
       </c>
       <c r="B26" t="n">
-        <v>92261</v>
+        <v>91545</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541931</v>
+        <v>541937</v>
       </c>
       <c r="R26" t="n">
-        <v>7192153</v>
+        <v>7192124</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,7 +3345,7 @@
         <v>129319225</v>
       </c>
       <c r="B27" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>129319244</v>
       </c>
       <c r="B28" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>129319235</v>
       </c>
       <c r="B29" t="n">
-        <v>95936</v>
+        <v>95938</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3663,10 +3663,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319236</v>
+        <v>129319233</v>
       </c>
       <c r="B30" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3674,21 +3674,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541880</v>
+        <v>541922</v>
       </c>
       <c r="R30" t="n">
-        <v>7192165</v>
+        <v>7192128</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3773,7 +3773,7 @@
         <v>129319227</v>
       </c>
       <c r="B31" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3877,10 +3877,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129319233</v>
+        <v>129319236</v>
       </c>
       <c r="B32" t="n">
-        <v>79043</v>
+        <v>80150</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,21 +3888,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541922</v>
+        <v>541880</v>
       </c>
       <c r="R32" t="n">
-        <v>7192128</v>
+        <v>7192165</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3987,7 +3987,7 @@
         <v>129319234</v>
       </c>
       <c r="B33" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129319232</v>
       </c>
       <c r="B2" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129319220</v>
       </c>
       <c r="B5" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319239</v>
+        <v>129319226</v>
       </c>
       <c r="B6" t="n">
-        <v>80150</v>
+        <v>82995</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541707</v>
+        <v>541943</v>
       </c>
       <c r="R6" t="n">
-        <v>7192111</v>
+        <v>7192145</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,32 +1206,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319226</v>
+        <v>129319239</v>
       </c>
       <c r="B7" t="n">
-        <v>82995</v>
+        <v>80150</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541943</v>
+        <v>541707</v>
       </c>
       <c r="R7" t="n">
-        <v>7192145</v>
+        <v>7192111</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129319229</v>
+        <v>129319218</v>
       </c>
       <c r="B9" t="n">
-        <v>91843</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1431,21 +1431,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541938</v>
+        <v>541948</v>
       </c>
       <c r="R9" t="n">
-        <v>7192121</v>
+        <v>7192187</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129319218</v>
+        <v>129319229</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>91847</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1538,21 +1538,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541948</v>
+        <v>541938</v>
       </c>
       <c r="R10" t="n">
-        <v>7192187</v>
+        <v>7192121</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319240</v>
+        <v>129319242</v>
       </c>
       <c r="B12" t="n">
-        <v>80150</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,34 +1752,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541698</v>
+        <v>541676</v>
       </c>
       <c r="R12" t="n">
-        <v>7192119</v>
+        <v>7192124</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1811,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1821,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129319242</v>
+        <v>129319240</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>80150</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1966,38 +1970,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541676</v>
+        <v>541698</v>
       </c>
       <c r="R14" t="n">
-        <v>7192124</v>
+        <v>7192119</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,7 +2176,7 @@
         <v>129319221</v>
       </c>
       <c r="B16" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>129319228</v>
       </c>
       <c r="B20" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>129319216</v>
       </c>
       <c r="B22" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,32 +2914,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319223</v>
+        <v>129319230</v>
       </c>
       <c r="B23" t="n">
-        <v>92263</v>
+        <v>91549</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541931</v>
+        <v>541937</v>
       </c>
       <c r="R23" t="n">
-        <v>7192153</v>
+        <v>7192124</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3021,32 +3021,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319213</v>
+        <v>129319225</v>
       </c>
       <c r="B24" t="n">
-        <v>92500</v>
+        <v>82878</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4769</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541932</v>
+        <v>541939</v>
       </c>
       <c r="R24" t="n">
-        <v>7192500</v>
+        <v>7192143</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3128,10 +3128,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129319231</v>
+        <v>129319244</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541937</v>
+        <v>541664</v>
       </c>
       <c r="R25" t="n">
         <v>7192124</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,10 +3235,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319230</v>
+        <v>129319231</v>
       </c>
       <c r="B26" t="n">
-        <v>91545</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3246,21 +3246,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3342,32 +3342,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319225</v>
+        <v>129319223</v>
       </c>
       <c r="B27" t="n">
-        <v>82878</v>
+        <v>92267</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541939</v>
+        <v>541931</v>
       </c>
       <c r="R27" t="n">
-        <v>7192143</v>
+        <v>7192153</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3449,32 +3449,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319244</v>
+        <v>129319213</v>
       </c>
       <c r="B28" t="n">
-        <v>80150</v>
+        <v>92504</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541664</v>
+        <v>541932</v>
       </c>
       <c r="R28" t="n">
-        <v>7192124</v>
+        <v>7192500</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3559,7 +3559,7 @@
         <v>129319235</v>
       </c>
       <c r="B29" t="n">
-        <v>95938</v>
+        <v>95942</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3663,10 +3663,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319233</v>
+        <v>129319236</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3674,21 +3674,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541922</v>
+        <v>541880</v>
       </c>
       <c r="R30" t="n">
-        <v>7192128</v>
+        <v>7192165</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3770,10 +3770,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129319227</v>
+        <v>129319234</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>91549</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3781,21 +3781,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541943</v>
+        <v>541913</v>
       </c>
       <c r="R31" t="n">
-        <v>7192145</v>
+        <v>7192150</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3877,10 +3877,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129319236</v>
+        <v>129319233</v>
       </c>
       <c r="B32" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,21 +3888,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541880</v>
+        <v>541922</v>
       </c>
       <c r="R32" t="n">
-        <v>7192165</v>
+        <v>7192128</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3984,10 +3984,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319234</v>
+        <v>129319227</v>
       </c>
       <c r="B33" t="n">
-        <v>91545</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,21 +3995,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541913</v>
+        <v>541943</v>
       </c>
       <c r="R33" t="n">
-        <v>7192150</v>
+        <v>7192145</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129319232</v>
       </c>
       <c r="B2" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319220</v>
+        <v>129319239</v>
       </c>
       <c r="B5" t="n">
-        <v>91569</v>
+        <v>80150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,19 +1007,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1027,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541916</v>
+        <v>541707</v>
       </c>
       <c r="R5" t="n">
-        <v>7192172</v>
+        <v>7192111</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1062,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1072,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,34 +1103,30 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319226</v>
+        <v>129319220</v>
       </c>
       <c r="B6" t="n">
-        <v>82995</v>
+        <v>91570</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541943</v>
+        <v>541916</v>
       </c>
       <c r="R6" t="n">
-        <v>7192145</v>
+        <v>7192172</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,32 +1206,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319239</v>
+        <v>129319226</v>
       </c>
       <c r="B7" t="n">
-        <v>80150</v>
+        <v>82995</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541707</v>
+        <v>541943</v>
       </c>
       <c r="R7" t="n">
-        <v>7192111</v>
+        <v>7192145</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1530,7 +1530,7 @@
         <v>129319229</v>
       </c>
       <c r="B10" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319242</v>
+        <v>129319240</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>80150</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,38 +1752,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541676</v>
+        <v>541698</v>
       </c>
       <c r="R12" t="n">
-        <v>7192124</v>
+        <v>7192119</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1815,7 +1811,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1821,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129319240</v>
+        <v>129319242</v>
       </c>
       <c r="B14" t="n">
-        <v>80150</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,34 +1966,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541698</v>
+        <v>541676</v>
       </c>
       <c r="R14" t="n">
-        <v>7192119</v>
+        <v>7192124</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,7 +2176,7 @@
         <v>129319221</v>
       </c>
       <c r="B16" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129319228</v>
+        <v>129319214</v>
       </c>
       <c r="B20" t="n">
-        <v>91569</v>
+        <v>80149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,19 +2612,23 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2632,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541949</v>
+        <v>541967</v>
       </c>
       <c r="R20" t="n">
-        <v>7192127</v>
+        <v>7192412</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2667,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2677,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129319214</v>
+        <v>129319228</v>
       </c>
       <c r="B21" t="n">
-        <v>80149</v>
+        <v>91570</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2715,23 +2719,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541967</v>
+        <v>541949</v>
       </c>
       <c r="R21" t="n">
-        <v>7192412</v>
+        <v>7192127</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2814,7 +2814,7 @@
         <v>129319216</v>
       </c>
       <c r="B22" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,10 +2914,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319230</v>
+        <v>129319231</v>
       </c>
       <c r="B23" t="n">
-        <v>91549</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2925,21 +2925,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319231</v>
+        <v>129319230</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3246,21 +3246,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3342,10 +3342,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319223</v>
+        <v>129319213</v>
       </c>
       <c r="B27" t="n">
-        <v>92267</v>
+        <v>92505</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3353,21 +3353,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>4769</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541931</v>
+        <v>541932</v>
       </c>
       <c r="R27" t="n">
-        <v>7192153</v>
+        <v>7192500</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3449,10 +3449,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319213</v>
+        <v>129319223</v>
       </c>
       <c r="B28" t="n">
-        <v>92504</v>
+        <v>92268</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3460,21 +3460,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541932</v>
+        <v>541931</v>
       </c>
       <c r="R28" t="n">
-        <v>7192500</v>
+        <v>7192153</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3559,7 +3559,7 @@
         <v>129319235</v>
       </c>
       <c r="B29" t="n">
-        <v>95942</v>
+        <v>95950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>129319234</v>
       </c>
       <c r="B31" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -1103,30 +1103,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319220</v>
+        <v>129319226</v>
       </c>
       <c r="B6" t="n">
-        <v>91570</v>
+        <v>82995</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1134,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541916</v>
+        <v>541943</v>
       </c>
       <c r="R6" t="n">
-        <v>7192172</v>
+        <v>7192145</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1169,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1179,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,34 +1210,30 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319226</v>
+        <v>129319220</v>
       </c>
       <c r="B7" t="n">
-        <v>82995</v>
+        <v>91570</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541943</v>
+        <v>541916</v>
       </c>
       <c r="R7" t="n">
-        <v>7192145</v>
+        <v>7192172</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129319218</v>
+        <v>129319229</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>91848</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1431,21 +1431,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541948</v>
+        <v>541938</v>
       </c>
       <c r="R9" t="n">
-        <v>7192187</v>
+        <v>7192121</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129319229</v>
+        <v>129319218</v>
       </c>
       <c r="B10" t="n">
-        <v>91848</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1538,21 +1538,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541938</v>
+        <v>541948</v>
       </c>
       <c r="R10" t="n">
-        <v>7192121</v>
+        <v>7192187</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319240</v>
+        <v>129319242</v>
       </c>
       <c r="B12" t="n">
-        <v>80150</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,34 +1752,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541698</v>
+        <v>541676</v>
       </c>
       <c r="R12" t="n">
-        <v>7192119</v>
+        <v>7192124</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1811,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1821,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129319215</v>
+        <v>129319240</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541988</v>
+        <v>541698</v>
       </c>
       <c r="R13" t="n">
-        <v>7192224</v>
+        <v>7192119</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1918,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1928,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129319242</v>
+        <v>129319215</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1966,38 +1970,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541676</v>
+        <v>541988</v>
       </c>
       <c r="R14" t="n">
-        <v>7192124</v>
+        <v>7192224</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2914,10 +2914,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319231</v>
+        <v>129319230</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2925,21 +2925,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3235,32 +3235,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319230</v>
+        <v>129319213</v>
       </c>
       <c r="B26" t="n">
-        <v>91550</v>
+        <v>92505</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541937</v>
+        <v>541932</v>
       </c>
       <c r="R26" t="n">
-        <v>7192124</v>
+        <v>7192500</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3342,10 +3342,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319213</v>
+        <v>129319223</v>
       </c>
       <c r="B27" t="n">
-        <v>92505</v>
+        <v>92268</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3353,21 +3353,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541932</v>
+        <v>541931</v>
       </c>
       <c r="R27" t="n">
-        <v>7192500</v>
+        <v>7192153</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3449,32 +3449,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319223</v>
+        <v>129319231</v>
       </c>
       <c r="B28" t="n">
-        <v>92268</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541931</v>
+        <v>541937</v>
       </c>
       <c r="R28" t="n">
-        <v>7192153</v>
+        <v>7192124</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3877,7 +3877,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129319233</v>
+        <v>129319227</v>
       </c>
       <c r="B32" t="n">
         <v>79044</v>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541922</v>
+        <v>541943</v>
       </c>
       <c r="R32" t="n">
-        <v>7192128</v>
+        <v>7192145</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3984,7 +3984,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319227</v>
+        <v>129319233</v>
       </c>
       <c r="B33" t="n">
         <v>79044</v>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541943</v>
+        <v>541922</v>
       </c>
       <c r="R33" t="n">
-        <v>7192145</v>
+        <v>7192128</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129319211</v>
+        <v>129319212</v>
       </c>
       <c r="B3" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541952</v>
+        <v>541941</v>
       </c>
       <c r="R3" t="n">
-        <v>7192657</v>
+        <v>7192545</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129319212</v>
+        <v>129319211</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541941</v>
+        <v>541952</v>
       </c>
       <c r="R4" t="n">
-        <v>7192545</v>
+        <v>7192657</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319239</v>
+        <v>129319226</v>
       </c>
       <c r="B5" t="n">
-        <v>80150</v>
+        <v>82995</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541707</v>
+        <v>541943</v>
       </c>
       <c r="R5" t="n">
-        <v>7192111</v>
+        <v>7192145</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,34 +1103,30 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319226</v>
+        <v>129319220</v>
       </c>
       <c r="B6" t="n">
-        <v>82995</v>
+        <v>91570</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1138,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541943</v>
+        <v>541916</v>
       </c>
       <c r="R6" t="n">
-        <v>7192145</v>
+        <v>7192172</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1173,7 +1169,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1179,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319220</v>
+        <v>129319239</v>
       </c>
       <c r="B7" t="n">
-        <v>91570</v>
+        <v>80150</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,19 +1217,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541916</v>
+        <v>541707</v>
       </c>
       <c r="R7" t="n">
-        <v>7192172</v>
+        <v>7192111</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319242</v>
+        <v>129319215</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,38 +1752,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541676</v>
+        <v>541988</v>
       </c>
       <c r="R12" t="n">
-        <v>7192124</v>
+        <v>7192224</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1815,7 +1811,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1821,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1848,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129319240</v>
+        <v>129319242</v>
       </c>
       <c r="B13" t="n">
-        <v>80150</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,34 +1859,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541698</v>
+        <v>541676</v>
       </c>
       <c r="R13" t="n">
-        <v>7192119</v>
+        <v>7192124</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129319215</v>
+        <v>129319240</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541988</v>
+        <v>541698</v>
       </c>
       <c r="R14" t="n">
-        <v>7192224</v>
+        <v>7192119</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129319232</v>
       </c>
       <c r="B2" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319220</v>
+        <v>129319239</v>
       </c>
       <c r="B6" t="n">
-        <v>91570</v>
+        <v>80150</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,19 +1114,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1134,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541916</v>
+        <v>541707</v>
       </c>
       <c r="R6" t="n">
-        <v>7192172</v>
+        <v>7192111</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1169,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1179,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319239</v>
+        <v>129319220</v>
       </c>
       <c r="B7" t="n">
-        <v>80150</v>
+        <v>91573</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,23 +1221,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541707</v>
+        <v>541916</v>
       </c>
       <c r="R7" t="n">
-        <v>7192111</v>
+        <v>7192172</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1423,7 +1423,7 @@
         <v>129319229</v>
       </c>
       <c r="B9" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129319242</v>
+        <v>129319240</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>80150</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,38 +1859,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541676</v>
+        <v>541698</v>
       </c>
       <c r="R13" t="n">
-        <v>7192124</v>
+        <v>7192119</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1922,7 +1918,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1928,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129319240</v>
+        <v>129319242</v>
       </c>
       <c r="B14" t="n">
-        <v>80150</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,34 +1966,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541698</v>
+        <v>541676</v>
       </c>
       <c r="R14" t="n">
-        <v>7192119</v>
+        <v>7192124</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,7 +2176,7 @@
         <v>129319221</v>
       </c>
       <c r="B16" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129319219</v>
+        <v>129319246</v>
       </c>
       <c r="B18" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541925</v>
+        <v>541653</v>
       </c>
       <c r="R18" t="n">
-        <v>7192171</v>
+        <v>7192124</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129319246</v>
+        <v>129319219</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541653</v>
+        <v>541925</v>
       </c>
       <c r="R19" t="n">
-        <v>7192124</v>
+        <v>7192171</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129319214</v>
+        <v>129319228</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>91573</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,23 +2612,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2636,10 +2632,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541967</v>
+        <v>541949</v>
       </c>
       <c r="R20" t="n">
-        <v>7192412</v>
+        <v>7192127</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2671,7 +2667,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2677,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129319228</v>
+        <v>129319214</v>
       </c>
       <c r="B21" t="n">
-        <v>91570</v>
+        <v>80149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,19 +2715,23 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541949</v>
+        <v>541967</v>
       </c>
       <c r="R21" t="n">
-        <v>7192127</v>
+        <v>7192412</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2814,7 +2814,7 @@
         <v>129319216</v>
       </c>
       <c r="B22" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,32 +2914,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319230</v>
+        <v>129319213</v>
       </c>
       <c r="B23" t="n">
-        <v>91550</v>
+        <v>92508</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541937</v>
+        <v>541932</v>
       </c>
       <c r="R23" t="n">
-        <v>7192124</v>
+        <v>7192500</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3021,10 +3021,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319225</v>
+        <v>129319231</v>
       </c>
       <c r="B24" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3032,21 +3032,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541939</v>
+        <v>541937</v>
       </c>
       <c r="R24" t="n">
-        <v>7192143</v>
+        <v>7192124</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3128,10 +3128,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129319244</v>
+        <v>129319225</v>
       </c>
       <c r="B25" t="n">
-        <v>80150</v>
+        <v>82878</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541664</v>
+        <v>541939</v>
       </c>
       <c r="R25" t="n">
-        <v>7192124</v>
+        <v>7192143</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,32 +3235,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319213</v>
+        <v>129319244</v>
       </c>
       <c r="B26" t="n">
-        <v>92505</v>
+        <v>80150</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4769</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541932</v>
+        <v>541664</v>
       </c>
       <c r="R26" t="n">
-        <v>7192500</v>
+        <v>7192124</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3342,32 +3342,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319223</v>
+        <v>129319230</v>
       </c>
       <c r="B27" t="n">
-        <v>92268</v>
+        <v>91553</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541931</v>
+        <v>541937</v>
       </c>
       <c r="R27" t="n">
-        <v>7192153</v>
+        <v>7192124</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3449,32 +3449,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319231</v>
+        <v>129319223</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>92271</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541937</v>
+        <v>541931</v>
       </c>
       <c r="R28" t="n">
-        <v>7192124</v>
+        <v>7192153</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3559,7 +3559,7 @@
         <v>129319235</v>
       </c>
       <c r="B29" t="n">
-        <v>95950</v>
+        <v>95953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>129319234</v>
       </c>
       <c r="B31" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129319227</v>
+        <v>129319233</v>
       </c>
       <c r="B32" t="n">
         <v>79044</v>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541943</v>
+        <v>541922</v>
       </c>
       <c r="R32" t="n">
-        <v>7192145</v>
+        <v>7192128</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3984,7 +3984,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319233</v>
+        <v>129319227</v>
       </c>
       <c r="B33" t="n">
         <v>79044</v>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541922</v>
+        <v>541943</v>
       </c>
       <c r="R33" t="n">
-        <v>7192128</v>
+        <v>7192145</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129319212</v>
+        <v>129319211</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541941</v>
+        <v>541952</v>
       </c>
       <c r="R3" t="n">
-        <v>7192545</v>
+        <v>7192657</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129319211</v>
+        <v>129319212</v>
       </c>
       <c r="B4" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541952</v>
+        <v>541941</v>
       </c>
       <c r="R4" t="n">
-        <v>7192657</v>
+        <v>7192545</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319226</v>
+        <v>129319239</v>
       </c>
       <c r="B5" t="n">
-        <v>82995</v>
+        <v>80150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541943</v>
+        <v>541707</v>
       </c>
       <c r="R5" t="n">
-        <v>7192145</v>
+        <v>7192111</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319239</v>
+        <v>129319220</v>
       </c>
       <c r="B6" t="n">
-        <v>80150</v>
+        <v>91573</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,23 +1114,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1138,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541707</v>
+        <v>541916</v>
       </c>
       <c r="R6" t="n">
-        <v>7192111</v>
+        <v>7192172</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1173,7 +1169,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1179,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,30 +1206,34 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319220</v>
+        <v>129319226</v>
       </c>
       <c r="B7" t="n">
-        <v>91573</v>
+        <v>82995</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541916</v>
+        <v>541943</v>
       </c>
       <c r="R7" t="n">
-        <v>7192172</v>
+        <v>7192145</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319215</v>
+        <v>129319240</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,21 +1752,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541988</v>
+        <v>541698</v>
       </c>
       <c r="R12" t="n">
-        <v>7192224</v>
+        <v>7192119</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,10 +1848,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129319240</v>
+        <v>129319215</v>
       </c>
       <c r="B13" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,21 +1859,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541698</v>
+        <v>541988</v>
       </c>
       <c r="R13" t="n">
-        <v>7192119</v>
+        <v>7192224</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129319246</v>
+        <v>129319219</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541653</v>
+        <v>541925</v>
       </c>
       <c r="R18" t="n">
-        <v>7192124</v>
+        <v>7192171</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129319219</v>
+        <v>129319246</v>
       </c>
       <c r="B19" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541925</v>
+        <v>541653</v>
       </c>
       <c r="R19" t="n">
-        <v>7192171</v>
+        <v>7192124</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2914,10 +2914,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319213</v>
+        <v>129319223</v>
       </c>
       <c r="B23" t="n">
-        <v>92508</v>
+        <v>92271</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2925,21 +2925,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541932</v>
+        <v>541931</v>
       </c>
       <c r="R23" t="n">
-        <v>7192500</v>
+        <v>7192153</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3021,10 +3021,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319231</v>
+        <v>129319230</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3032,21 +3032,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3342,32 +3342,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319230</v>
+        <v>129319213</v>
       </c>
       <c r="B27" t="n">
-        <v>91553</v>
+        <v>92508</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541937</v>
+        <v>541932</v>
       </c>
       <c r="R27" t="n">
-        <v>7192124</v>
+        <v>7192500</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3449,32 +3449,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319223</v>
+        <v>129319231</v>
       </c>
       <c r="B28" t="n">
-        <v>92271</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541931</v>
+        <v>541937</v>
       </c>
       <c r="R28" t="n">
-        <v>7192153</v>
+        <v>7192124</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129319219</v>
+        <v>129319246</v>
       </c>
       <c r="B18" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541925</v>
+        <v>541653</v>
       </c>
       <c r="R18" t="n">
-        <v>7192171</v>
+        <v>7192124</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129319246</v>
+        <v>129319219</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541653</v>
+        <v>541925</v>
       </c>
       <c r="R19" t="n">
-        <v>7192124</v>
+        <v>7192171</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2914,32 +2914,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319223</v>
+        <v>129319230</v>
       </c>
       <c r="B23" t="n">
-        <v>92271</v>
+        <v>91553</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541931</v>
+        <v>541937</v>
       </c>
       <c r="R23" t="n">
-        <v>7192153</v>
+        <v>7192124</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3021,10 +3021,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319230</v>
+        <v>129319225</v>
       </c>
       <c r="B24" t="n">
-        <v>91553</v>
+        <v>82878</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3032,21 +3032,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541937</v>
+        <v>541939</v>
       </c>
       <c r="R24" t="n">
-        <v>7192124</v>
+        <v>7192143</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3128,10 +3128,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129319225</v>
+        <v>129319244</v>
       </c>
       <c r="B25" t="n">
-        <v>82878</v>
+        <v>80150</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541939</v>
+        <v>541664</v>
       </c>
       <c r="R25" t="n">
-        <v>7192143</v>
+        <v>7192124</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,10 +3235,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319244</v>
+        <v>129319231</v>
       </c>
       <c r="B26" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3246,21 +3246,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541664</v>
+        <v>541937</v>
       </c>
       <c r="R26" t="n">
         <v>7192124</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3449,32 +3449,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319231</v>
+        <v>129319223</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>92271</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541937</v>
+        <v>541931</v>
       </c>
       <c r="R28" t="n">
-        <v>7192124</v>
+        <v>7192153</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129319211</v>
+        <v>129319212</v>
       </c>
       <c r="B3" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541952</v>
+        <v>541941</v>
       </c>
       <c r="R3" t="n">
-        <v>7192657</v>
+        <v>7192545</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129319212</v>
+        <v>129319211</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541941</v>
+        <v>541952</v>
       </c>
       <c r="R4" t="n">
-        <v>7192545</v>
+        <v>7192657</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319239</v>
+        <v>129319220</v>
       </c>
       <c r="B5" t="n">
-        <v>80150</v>
+        <v>91573</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,23 +1007,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1031,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541707</v>
+        <v>541916</v>
       </c>
       <c r="R5" t="n">
-        <v>7192111</v>
+        <v>7192172</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,7 +1062,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1072,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,30 +1099,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319220</v>
+        <v>129319226</v>
       </c>
       <c r="B6" t="n">
-        <v>91573</v>
+        <v>82995</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541916</v>
+        <v>541943</v>
       </c>
       <c r="R6" t="n">
-        <v>7192172</v>
+        <v>7192145</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,32 +1206,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319226</v>
+        <v>129319239</v>
       </c>
       <c r="B7" t="n">
-        <v>82995</v>
+        <v>80150</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541943</v>
+        <v>541707</v>
       </c>
       <c r="R7" t="n">
-        <v>7192145</v>
+        <v>7192111</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129319246</v>
+        <v>129319219</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541653</v>
+        <v>541925</v>
       </c>
       <c r="R18" t="n">
-        <v>7192124</v>
+        <v>7192171</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129319219</v>
+        <v>129319246</v>
       </c>
       <c r="B19" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541925</v>
+        <v>541653</v>
       </c>
       <c r="R19" t="n">
-        <v>7192171</v>
+        <v>7192124</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2914,32 +2914,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319230</v>
+        <v>129319213</v>
       </c>
       <c r="B23" t="n">
-        <v>91553</v>
+        <v>92508</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541937</v>
+        <v>541932</v>
       </c>
       <c r="R23" t="n">
-        <v>7192124</v>
+        <v>7192500</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3021,10 +3021,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319225</v>
+        <v>129319231</v>
       </c>
       <c r="B24" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3032,21 +3032,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541939</v>
+        <v>541937</v>
       </c>
       <c r="R24" t="n">
-        <v>7192143</v>
+        <v>7192124</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3128,10 +3128,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129319244</v>
+        <v>129319230</v>
       </c>
       <c r="B25" t="n">
-        <v>80150</v>
+        <v>91553</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541664</v>
+        <v>541937</v>
       </c>
       <c r="R25" t="n">
         <v>7192124</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,10 +3235,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319231</v>
+        <v>129319225</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3246,21 +3246,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541937</v>
+        <v>541939</v>
       </c>
       <c r="R26" t="n">
-        <v>7192124</v>
+        <v>7192143</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3342,32 +3342,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319213</v>
+        <v>129319244</v>
       </c>
       <c r="B27" t="n">
-        <v>92508</v>
+        <v>80150</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4769</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541932</v>
+        <v>541664</v>
       </c>
       <c r="R27" t="n">
-        <v>7192500</v>
+        <v>7192124</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3663,10 +3663,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319236</v>
+        <v>129319233</v>
       </c>
       <c r="B30" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3674,21 +3674,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541880</v>
+        <v>541922</v>
       </c>
       <c r="R30" t="n">
-        <v>7192165</v>
+        <v>7192128</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3770,10 +3770,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129319234</v>
+        <v>129319227</v>
       </c>
       <c r="B31" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3781,21 +3781,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541913</v>
+        <v>541943</v>
       </c>
       <c r="R31" t="n">
-        <v>7192150</v>
+        <v>7192145</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3877,10 +3877,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129319233</v>
+        <v>129319236</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,21 +3888,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541922</v>
+        <v>541880</v>
       </c>
       <c r="R32" t="n">
-        <v>7192128</v>
+        <v>7192165</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3984,10 +3984,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319227</v>
+        <v>129319234</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,21 +3995,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541943</v>
+        <v>541913</v>
       </c>
       <c r="R33" t="n">
-        <v>7192145</v>
+        <v>7192150</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129319212</v>
+        <v>129319211</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541941</v>
+        <v>541952</v>
       </c>
       <c r="R3" t="n">
-        <v>7192545</v>
+        <v>7192657</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129319211</v>
+        <v>129319212</v>
       </c>
       <c r="B4" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541952</v>
+        <v>541941</v>
       </c>
       <c r="R4" t="n">
-        <v>7192657</v>
+        <v>7192545</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319226</v>
+        <v>129319239</v>
       </c>
       <c r="B6" t="n">
-        <v>82995</v>
+        <v>80150</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541943</v>
+        <v>541707</v>
       </c>
       <c r="R6" t="n">
-        <v>7192145</v>
+        <v>7192111</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,32 +1206,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319239</v>
+        <v>129319226</v>
       </c>
       <c r="B7" t="n">
-        <v>80150</v>
+        <v>82995</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541707</v>
+        <v>541943</v>
       </c>
       <c r="R7" t="n">
-        <v>7192111</v>
+        <v>7192145</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129319219</v>
+        <v>129319246</v>
       </c>
       <c r="B18" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541925</v>
+        <v>541653</v>
       </c>
       <c r="R18" t="n">
-        <v>7192171</v>
+        <v>7192124</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129319246</v>
+        <v>129319219</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541653</v>
+        <v>541925</v>
       </c>
       <c r="R19" t="n">
-        <v>7192124</v>
+        <v>7192171</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3021,32 +3021,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319231</v>
+        <v>129319223</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>92271</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541937</v>
+        <v>541931</v>
       </c>
       <c r="R24" t="n">
-        <v>7192124</v>
+        <v>7192153</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3449,32 +3449,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319223</v>
+        <v>129319231</v>
       </c>
       <c r="B28" t="n">
-        <v>92271</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541931</v>
+        <v>541937</v>
       </c>
       <c r="R28" t="n">
-        <v>7192153</v>
+        <v>7192124</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3663,10 +3663,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319233</v>
+        <v>129319236</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3674,21 +3674,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541922</v>
+        <v>541880</v>
       </c>
       <c r="R30" t="n">
-        <v>7192128</v>
+        <v>7192165</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3770,10 +3770,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129319227</v>
+        <v>129319234</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3781,21 +3781,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541943</v>
+        <v>541913</v>
       </c>
       <c r="R31" t="n">
-        <v>7192145</v>
+        <v>7192150</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3877,10 +3877,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129319236</v>
+        <v>129319233</v>
       </c>
       <c r="B32" t="n">
-        <v>80150</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,21 +3888,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541880</v>
+        <v>541922</v>
       </c>
       <c r="R32" t="n">
-        <v>7192165</v>
+        <v>7192128</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3984,10 +3984,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319234</v>
+        <v>129319227</v>
       </c>
       <c r="B33" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,21 +3995,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541913</v>
+        <v>541943</v>
       </c>
       <c r="R33" t="n">
-        <v>7192150</v>
+        <v>7192145</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319220</v>
+        <v>129319239</v>
       </c>
       <c r="B5" t="n">
-        <v>91573</v>
+        <v>80150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,19 +1007,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1027,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541916</v>
+        <v>541707</v>
       </c>
       <c r="R5" t="n">
-        <v>7192172</v>
+        <v>7192111</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1062,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1072,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319239</v>
+        <v>129319220</v>
       </c>
       <c r="B6" t="n">
-        <v>80150</v>
+        <v>91573</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,23 +1114,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541707</v>
+        <v>541916</v>
       </c>
       <c r="R6" t="n">
-        <v>7192111</v>
+        <v>7192172</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129319246</v>
+        <v>129319219</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>82878</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541653</v>
+        <v>541925</v>
       </c>
       <c r="R18" t="n">
-        <v>7192124</v>
+        <v>7192171</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129319219</v>
+        <v>129319246</v>
       </c>
       <c r="B19" t="n">
-        <v>82878</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541925</v>
+        <v>541653</v>
       </c>
       <c r="R19" t="n">
-        <v>7192171</v>
+        <v>7192124</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2914,10 +2914,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319213</v>
+        <v>129319223</v>
       </c>
       <c r="B23" t="n">
-        <v>92508</v>
+        <v>92271</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2925,21 +2925,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541932</v>
+        <v>541931</v>
       </c>
       <c r="R23" t="n">
-        <v>7192500</v>
+        <v>7192153</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3021,32 +3021,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319223</v>
+        <v>129319244</v>
       </c>
       <c r="B24" t="n">
-        <v>92271</v>
+        <v>80150</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541931</v>
+        <v>541664</v>
       </c>
       <c r="R24" t="n">
-        <v>7192153</v>
+        <v>7192124</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3342,32 +3342,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319244</v>
+        <v>129319213</v>
       </c>
       <c r="B27" t="n">
-        <v>80150</v>
+        <v>92508</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>4769</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541664</v>
+        <v>541932</v>
       </c>
       <c r="R27" t="n">
-        <v>7192124</v>
+        <v>7192500</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3663,10 +3663,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319236</v>
+        <v>129319234</v>
       </c>
       <c r="B30" t="n">
-        <v>80150</v>
+        <v>91553</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3674,21 +3674,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541880</v>
+        <v>541913</v>
       </c>
       <c r="R30" t="n">
-        <v>7192165</v>
+        <v>7192150</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3770,10 +3770,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129319234</v>
+        <v>129319233</v>
       </c>
       <c r="B31" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3781,21 +3781,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541913</v>
+        <v>541922</v>
       </c>
       <c r="R31" t="n">
-        <v>7192150</v>
+        <v>7192128</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3877,7 +3877,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129319233</v>
+        <v>129319227</v>
       </c>
       <c r="B32" t="n">
         <v>79044</v>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541922</v>
+        <v>541943</v>
       </c>
       <c r="R32" t="n">
-        <v>7192128</v>
+        <v>7192145</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3984,10 +3984,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319227</v>
+        <v>129319236</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>80150</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,21 +3995,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541943</v>
+        <v>541880</v>
       </c>
       <c r="R33" t="n">
-        <v>7192145</v>
+        <v>7192165</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129319232</v>
       </c>
       <c r="B2" t="n">
-        <v>91851</v>
+        <v>91879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129319211</v>
       </c>
       <c r="B3" t="n">
-        <v>80150</v>
+        <v>80176</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129319212</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319239</v>
+        <v>129319220</v>
       </c>
       <c r="B5" t="n">
-        <v>80150</v>
+        <v>91601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,23 +1007,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1031,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541707</v>
+        <v>541916</v>
       </c>
       <c r="R5" t="n">
-        <v>7192111</v>
+        <v>7192172</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,7 +1062,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1072,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319220</v>
+        <v>129319239</v>
       </c>
       <c r="B6" t="n">
-        <v>91573</v>
+        <v>80176</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,19 +1110,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541916</v>
+        <v>541707</v>
       </c>
       <c r="R6" t="n">
-        <v>7192172</v>
+        <v>7192111</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,7 +1209,7 @@
         <v>129319226</v>
       </c>
       <c r="B7" t="n">
-        <v>82995</v>
+        <v>83022</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>129319222</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129319229</v>
+        <v>129319218</v>
       </c>
       <c r="B9" t="n">
-        <v>91851</v>
+        <v>79070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1431,21 +1431,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541938</v>
+        <v>541948</v>
       </c>
       <c r="R9" t="n">
-        <v>7192121</v>
+        <v>7192187</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129319218</v>
+        <v>129319229</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>91879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1538,21 +1538,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541948</v>
+        <v>541938</v>
       </c>
       <c r="R10" t="n">
-        <v>7192187</v>
+        <v>7192121</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1637,7 +1637,7 @@
         <v>129319224</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319240</v>
+        <v>129319242</v>
       </c>
       <c r="B12" t="n">
-        <v>80150</v>
+        <v>57890</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,34 +1752,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541698</v>
+        <v>541676</v>
       </c>
       <c r="R12" t="n">
-        <v>7192119</v>
+        <v>7192124</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1811,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1821,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129319215</v>
+        <v>129319240</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>80176</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541988</v>
+        <v>541698</v>
       </c>
       <c r="R13" t="n">
-        <v>7192224</v>
+        <v>7192119</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1918,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1928,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129319242</v>
+        <v>129319215</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>79070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1966,38 +1970,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541676</v>
+        <v>541988</v>
       </c>
       <c r="R14" t="n">
-        <v>7192124</v>
+        <v>7192224</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,7 +2069,7 @@
         <v>129319238</v>
       </c>
       <c r="B15" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>129319221</v>
       </c>
       <c r="B16" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>129319237</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129319219</v>
+        <v>129319246</v>
       </c>
       <c r="B18" t="n">
-        <v>82878</v>
+        <v>79070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541925</v>
+        <v>541653</v>
       </c>
       <c r="R18" t="n">
-        <v>7192171</v>
+        <v>7192124</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129319246</v>
+        <v>129319219</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>82905</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541653</v>
+        <v>541925</v>
       </c>
       <c r="R19" t="n">
-        <v>7192124</v>
+        <v>7192171</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129319228</v>
+        <v>129319214</v>
       </c>
       <c r="B20" t="n">
-        <v>91573</v>
+        <v>80175</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,19 +2612,23 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2632,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541949</v>
+        <v>541967</v>
       </c>
       <c r="R20" t="n">
-        <v>7192127</v>
+        <v>7192412</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2667,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2677,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129319214</v>
+        <v>129319228</v>
       </c>
       <c r="B21" t="n">
-        <v>80149</v>
+        <v>91601</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2715,23 +2719,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541967</v>
+        <v>541949</v>
       </c>
       <c r="R21" t="n">
-        <v>7192412</v>
+        <v>7192127</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2814,7 +2814,7 @@
         <v>129319216</v>
       </c>
       <c r="B22" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,32 +2914,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319223</v>
+        <v>129319225</v>
       </c>
       <c r="B23" t="n">
-        <v>92271</v>
+        <v>82905</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541931</v>
+        <v>541939</v>
       </c>
       <c r="R23" t="n">
-        <v>7192153</v>
+        <v>7192143</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3024,7 +3024,7 @@
         <v>129319244</v>
       </c>
       <c r="B24" t="n">
-        <v>80150</v>
+        <v>80176</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>129319230</v>
       </c>
       <c r="B25" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3235,32 +3235,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319225</v>
+        <v>129319223</v>
       </c>
       <c r="B26" t="n">
-        <v>82878</v>
+        <v>92299</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541939</v>
+        <v>541931</v>
       </c>
       <c r="R26" t="n">
-        <v>7192143</v>
+        <v>7192153</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3342,32 +3342,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319213</v>
+        <v>129319231</v>
       </c>
       <c r="B27" t="n">
-        <v>92508</v>
+        <v>79070</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541932</v>
+        <v>541937</v>
       </c>
       <c r="R27" t="n">
-        <v>7192500</v>
+        <v>7192124</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3449,32 +3449,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319231</v>
+        <v>129319213</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>92536</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541937</v>
+        <v>541932</v>
       </c>
       <c r="R28" t="n">
-        <v>7192124</v>
+        <v>7192500</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3559,7 +3559,7 @@
         <v>129319235</v>
       </c>
       <c r="B29" t="n">
-        <v>95953</v>
+        <v>95982</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3663,10 +3663,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319234</v>
+        <v>129319236</v>
       </c>
       <c r="B30" t="n">
-        <v>91553</v>
+        <v>80176</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3674,21 +3674,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541913</v>
+        <v>541880</v>
       </c>
       <c r="R30" t="n">
-        <v>7192150</v>
+        <v>7192165</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3770,10 +3770,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129319233</v>
+        <v>129319234</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>91581</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3781,21 +3781,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541922</v>
+        <v>541913</v>
       </c>
       <c r="R31" t="n">
-        <v>7192128</v>
+        <v>7192150</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3877,10 +3877,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129319227</v>
+        <v>129319233</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541943</v>
+        <v>541922</v>
       </c>
       <c r="R32" t="n">
-        <v>7192145</v>
+        <v>7192128</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3984,10 +3984,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319236</v>
+        <v>129319227</v>
       </c>
       <c r="B33" t="n">
-        <v>80150</v>
+        <v>79070</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,21 +3995,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541880</v>
+        <v>541943</v>
       </c>
       <c r="R33" t="n">
-        <v>7192165</v>
+        <v>7192145</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319220</v>
+        <v>129319239</v>
       </c>
       <c r="B5" t="n">
-        <v>91601</v>
+        <v>80176</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,19 +1007,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1027,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541916</v>
+        <v>541707</v>
       </c>
       <c r="R5" t="n">
-        <v>7192172</v>
+        <v>7192111</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1062,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1072,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,32 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319239</v>
+        <v>129319226</v>
       </c>
       <c r="B6" t="n">
-        <v>80176</v>
+        <v>83022</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541707</v>
+        <v>541943</v>
       </c>
       <c r="R6" t="n">
-        <v>7192111</v>
+        <v>7192145</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1169,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1179,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,34 +1210,30 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319226</v>
+        <v>129319220</v>
       </c>
       <c r="B7" t="n">
-        <v>83022</v>
+        <v>91601</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541943</v>
+        <v>541916</v>
       </c>
       <c r="R7" t="n">
-        <v>7192145</v>
+        <v>7192172</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129319218</v>
+        <v>129319229</v>
       </c>
       <c r="B9" t="n">
-        <v>79070</v>
+        <v>91879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1431,21 +1431,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541948</v>
+        <v>541938</v>
       </c>
       <c r="R9" t="n">
-        <v>7192187</v>
+        <v>7192121</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129319229</v>
+        <v>129319218</v>
       </c>
       <c r="B10" t="n">
-        <v>91879</v>
+        <v>79070</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1538,21 +1538,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541938</v>
+        <v>541948</v>
       </c>
       <c r="R10" t="n">
-        <v>7192121</v>
+        <v>7192187</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129319214</v>
+        <v>129319228</v>
       </c>
       <c r="B20" t="n">
-        <v>80175</v>
+        <v>91601</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,23 +2612,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2636,10 +2632,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541967</v>
+        <v>541949</v>
       </c>
       <c r="R20" t="n">
-        <v>7192412</v>
+        <v>7192127</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2671,7 +2667,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2677,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129319228</v>
+        <v>129319214</v>
       </c>
       <c r="B21" t="n">
-        <v>91601</v>
+        <v>80175</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2719,19 +2715,23 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541949</v>
+        <v>541967</v>
       </c>
       <c r="R21" t="n">
-        <v>7192127</v>
+        <v>7192412</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2914,32 +2914,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319225</v>
+        <v>129319223</v>
       </c>
       <c r="B23" t="n">
-        <v>82905</v>
+        <v>92299</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541939</v>
+        <v>541931</v>
       </c>
       <c r="R23" t="n">
-        <v>7192143</v>
+        <v>7192153</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3021,10 +3021,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319244</v>
+        <v>129319225</v>
       </c>
       <c r="B24" t="n">
-        <v>80176</v>
+        <v>82905</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3032,21 +3032,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541664</v>
+        <v>541939</v>
       </c>
       <c r="R24" t="n">
-        <v>7192124</v>
+        <v>7192143</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3128,10 +3128,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129319230</v>
+        <v>129319244</v>
       </c>
       <c r="B25" t="n">
-        <v>91581</v>
+        <v>80176</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541937</v>
+        <v>541664</v>
       </c>
       <c r="R25" t="n">
         <v>7192124</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,32 +3235,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319223</v>
+        <v>129319230</v>
       </c>
       <c r="B26" t="n">
-        <v>92299</v>
+        <v>91581</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541931</v>
+        <v>541937</v>
       </c>
       <c r="R26" t="n">
-        <v>7192153</v>
+        <v>7192124</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3342,32 +3342,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319231</v>
+        <v>129319213</v>
       </c>
       <c r="B27" t="n">
-        <v>79070</v>
+        <v>92536</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541937</v>
+        <v>541932</v>
       </c>
       <c r="R27" t="n">
-        <v>7192124</v>
+        <v>7192500</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3449,32 +3449,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319213</v>
+        <v>129319231</v>
       </c>
       <c r="B28" t="n">
-        <v>92536</v>
+        <v>79070</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541932</v>
+        <v>541937</v>
       </c>
       <c r="R28" t="n">
-        <v>7192500</v>
+        <v>7192124</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129319232</v>
       </c>
       <c r="B2" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129319211</v>
       </c>
       <c r="B3" t="n">
-        <v>80176</v>
+        <v>80181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129319212</v>
       </c>
       <c r="B4" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129319239</v>
       </c>
       <c r="B5" t="n">
-        <v>80176</v>
+        <v>80181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,34 +1103,30 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319226</v>
+        <v>129319220</v>
       </c>
       <c r="B6" t="n">
-        <v>83022</v>
+        <v>91607</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1138,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541943</v>
+        <v>541916</v>
       </c>
       <c r="R6" t="n">
-        <v>7192145</v>
+        <v>7192172</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1173,7 +1169,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1179,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,30 +1206,34 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319220</v>
+        <v>129319226</v>
       </c>
       <c r="B7" t="n">
-        <v>91601</v>
+        <v>83027</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541916</v>
+        <v>541943</v>
       </c>
       <c r="R7" t="n">
-        <v>7192172</v>
+        <v>7192145</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,7 +1316,7 @@
         <v>129319222</v>
       </c>
       <c r="B8" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>129319229</v>
       </c>
       <c r="B9" t="n">
-        <v>91879</v>
+        <v>91885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129319218</v>
       </c>
       <c r="B10" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>129319224</v>
       </c>
       <c r="B11" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319242</v>
+        <v>129319240</v>
       </c>
       <c r="B12" t="n">
-        <v>57890</v>
+        <v>80181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,38 +1752,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541676</v>
+        <v>541698</v>
       </c>
       <c r="R12" t="n">
-        <v>7192124</v>
+        <v>7192119</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1815,7 +1811,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1821,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1848,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129319240</v>
+        <v>129319215</v>
       </c>
       <c r="B13" t="n">
-        <v>80176</v>
+        <v>79075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,21 +1859,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1883,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541698</v>
+        <v>541988</v>
       </c>
       <c r="R13" t="n">
-        <v>7192119</v>
+        <v>7192224</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1922,7 +1918,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1928,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129319215</v>
+        <v>129319242</v>
       </c>
       <c r="B14" t="n">
-        <v>79070</v>
+        <v>57895</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,34 +1966,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541988</v>
+        <v>541676</v>
       </c>
       <c r="R14" t="n">
-        <v>7192224</v>
+        <v>7192124</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,7 +2069,7 @@
         <v>129319238</v>
       </c>
       <c r="B15" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>129319221</v>
       </c>
       <c r="B16" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>129319237</v>
       </c>
       <c r="B17" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129319246</v>
+        <v>129319219</v>
       </c>
       <c r="B18" t="n">
-        <v>79070</v>
+        <v>82910</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541653</v>
+        <v>541925</v>
       </c>
       <c r="R18" t="n">
-        <v>7192124</v>
+        <v>7192171</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129319219</v>
+        <v>129319246</v>
       </c>
       <c r="B19" t="n">
-        <v>82905</v>
+        <v>79075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2505,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541925</v>
+        <v>541653</v>
       </c>
       <c r="R19" t="n">
-        <v>7192171</v>
+        <v>7192124</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2604,7 +2604,7 @@
         <v>129319228</v>
       </c>
       <c r="B20" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>129319214</v>
       </c>
       <c r="B21" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>129319216</v>
       </c>
       <c r="B22" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,32 +2914,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319223</v>
+        <v>129319230</v>
       </c>
       <c r="B23" t="n">
-        <v>92299</v>
+        <v>91587</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541931</v>
+        <v>541937</v>
       </c>
       <c r="R23" t="n">
-        <v>7192153</v>
+        <v>7192124</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3024,7 +3024,7 @@
         <v>129319225</v>
       </c>
       <c r="B24" t="n">
-        <v>82905</v>
+        <v>82910</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
         <v>129319244</v>
       </c>
       <c r="B25" t="n">
-        <v>80176</v>
+        <v>80181</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3235,32 +3235,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319230</v>
+        <v>129319223</v>
       </c>
       <c r="B26" t="n">
-        <v>91581</v>
+        <v>92305</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541937</v>
+        <v>541931</v>
       </c>
       <c r="R26" t="n">
-        <v>7192124</v>
+        <v>7192153</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3342,32 +3342,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319213</v>
+        <v>129319231</v>
       </c>
       <c r="B27" t="n">
-        <v>92536</v>
+        <v>79075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541932</v>
+        <v>541937</v>
       </c>
       <c r="R27" t="n">
-        <v>7192500</v>
+        <v>7192124</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3449,32 +3449,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319231</v>
+        <v>129319213</v>
       </c>
       <c r="B28" t="n">
-        <v>79070</v>
+        <v>92542</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541937</v>
+        <v>541932</v>
       </c>
       <c r="R28" t="n">
-        <v>7192124</v>
+        <v>7192500</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3559,7 +3559,7 @@
         <v>129319235</v>
       </c>
       <c r="B29" t="n">
-        <v>95982</v>
+        <v>95994</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3663,10 +3663,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319236</v>
+        <v>129319234</v>
       </c>
       <c r="B30" t="n">
-        <v>80176</v>
+        <v>91587</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3674,21 +3674,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541880</v>
+        <v>541913</v>
       </c>
       <c r="R30" t="n">
-        <v>7192165</v>
+        <v>7192150</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3770,10 +3770,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129319234</v>
+        <v>129319236</v>
       </c>
       <c r="B31" t="n">
-        <v>91581</v>
+        <v>80181</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3781,21 +3781,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541913</v>
+        <v>541880</v>
       </c>
       <c r="R31" t="n">
-        <v>7192150</v>
+        <v>7192165</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3880,7 +3880,7 @@
         <v>129319233</v>
       </c>
       <c r="B32" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>129319227</v>
       </c>
       <c r="B33" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129319232</v>
       </c>
       <c r="B2" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129319211</v>
       </c>
       <c r="B3" t="n">
-        <v>80181</v>
+        <v>80182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129319212</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319239</v>
+        <v>129319226</v>
       </c>
       <c r="B5" t="n">
-        <v>80181</v>
+        <v>83028</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541707</v>
+        <v>541943</v>
       </c>
       <c r="R5" t="n">
-        <v>7192111</v>
+        <v>7192145</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>129319220</v>
       </c>
       <c r="B6" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,32 +1206,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319226</v>
+        <v>129319239</v>
       </c>
       <c r="B7" t="n">
-        <v>83027</v>
+        <v>80182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541943</v>
+        <v>541707</v>
       </c>
       <c r="R7" t="n">
-        <v>7192145</v>
+        <v>7192111</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,7 +1316,7 @@
         <v>129319222</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>129319229</v>
       </c>
       <c r="B9" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
         <v>129319218</v>
       </c>
       <c r="B10" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>129319224</v>
       </c>
       <c r="B11" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>129319240</v>
       </c>
       <c r="B12" t="n">
-        <v>80181</v>
+        <v>80182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,10 +1848,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129319215</v>
+        <v>129319242</v>
       </c>
       <c r="B13" t="n">
-        <v>79075</v>
+        <v>57896</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,34 +1859,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541988</v>
+        <v>541676</v>
       </c>
       <c r="R13" t="n">
-        <v>7192224</v>
+        <v>7192124</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1918,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1928,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129319242</v>
+        <v>129319215</v>
       </c>
       <c r="B14" t="n">
-        <v>57895</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1966,38 +1970,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541676</v>
+        <v>541988</v>
       </c>
       <c r="R14" t="n">
-        <v>7192124</v>
+        <v>7192224</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,7 +2069,7 @@
         <v>129319238</v>
       </c>
       <c r="B15" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>129319221</v>
       </c>
       <c r="B16" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>129319237</v>
       </c>
       <c r="B17" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129319219</v>
       </c>
       <c r="B18" t="n">
-        <v>82910</v>
+        <v>82911</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>129319246</v>
       </c>
       <c r="B19" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>129319228</v>
       </c>
       <c r="B20" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>129319214</v>
       </c>
       <c r="B21" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>129319216</v>
       </c>
       <c r="B22" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,10 +2914,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319230</v>
+        <v>129319231</v>
       </c>
       <c r="B23" t="n">
-        <v>91587</v>
+        <v>79076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2925,21 +2925,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3021,32 +3021,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319225</v>
+        <v>129319213</v>
       </c>
       <c r="B24" t="n">
-        <v>82910</v>
+        <v>92543</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541939</v>
+        <v>541932</v>
       </c>
       <c r="R24" t="n">
-        <v>7192143</v>
+        <v>7192500</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3128,10 +3128,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129319244</v>
+        <v>129319230</v>
       </c>
       <c r="B25" t="n">
-        <v>80181</v>
+        <v>91588</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3139,21 +3139,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541664</v>
+        <v>541937</v>
       </c>
       <c r="R25" t="n">
         <v>7192124</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,32 +3235,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319223</v>
+        <v>129319225</v>
       </c>
       <c r="B26" t="n">
-        <v>92305</v>
+        <v>82911</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541931</v>
+        <v>541939</v>
       </c>
       <c r="R26" t="n">
-        <v>7192153</v>
+        <v>7192143</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3342,10 +3342,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319231</v>
+        <v>129319244</v>
       </c>
       <c r="B27" t="n">
-        <v>79075</v>
+        <v>80182</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3353,21 +3353,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541937</v>
+        <v>541664</v>
       </c>
       <c r="R27" t="n">
         <v>7192124</v>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3449,10 +3449,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319213</v>
+        <v>129319223</v>
       </c>
       <c r="B28" t="n">
-        <v>92542</v>
+        <v>92306</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3460,21 +3460,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541932</v>
+        <v>541931</v>
       </c>
       <c r="R28" t="n">
-        <v>7192500</v>
+        <v>7192153</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3559,7 +3559,7 @@
         <v>129319235</v>
       </c>
       <c r="B29" t="n">
-        <v>95994</v>
+        <v>95995</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>129319234</v>
       </c>
       <c r="B30" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3770,10 +3770,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129319236</v>
+        <v>129319233</v>
       </c>
       <c r="B31" t="n">
-        <v>80181</v>
+        <v>79076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3781,21 +3781,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541880</v>
+        <v>541922</v>
       </c>
       <c r="R31" t="n">
-        <v>7192165</v>
+        <v>7192128</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3877,10 +3877,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129319233</v>
+        <v>129319227</v>
       </c>
       <c r="B32" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541922</v>
+        <v>541943</v>
       </c>
       <c r="R32" t="n">
-        <v>7192128</v>
+        <v>7192145</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3984,10 +3984,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319227</v>
+        <v>129319236</v>
       </c>
       <c r="B33" t="n">
-        <v>79075</v>
+        <v>80182</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,21 +3995,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541943</v>
+        <v>541880</v>
       </c>
       <c r="R33" t="n">
-        <v>7192145</v>
+        <v>7192165</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -996,34 +996,30 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319226</v>
+        <v>129319220</v>
       </c>
       <c r="B5" t="n">
-        <v>83028</v>
+        <v>91608</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1031,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541943</v>
+        <v>541916</v>
       </c>
       <c r="R5" t="n">
-        <v>7192145</v>
+        <v>7192172</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,7 +1062,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1072,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319220</v>
+        <v>129319239</v>
       </c>
       <c r="B6" t="n">
-        <v>91608</v>
+        <v>80182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,19 +1110,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541916</v>
+        <v>541707</v>
       </c>
       <c r="R6" t="n">
-        <v>7192172</v>
+        <v>7192111</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,32 +1206,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319239</v>
+        <v>129319226</v>
       </c>
       <c r="B7" t="n">
-        <v>80182</v>
+        <v>83028</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541707</v>
+        <v>541943</v>
       </c>
       <c r="R7" t="n">
-        <v>7192111</v>
+        <v>7192145</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129319232</v>
       </c>
       <c r="B2" t="n">
-        <v>91886</v>
+        <v>91891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129319211</v>
+        <v>129319212</v>
       </c>
       <c r="B3" t="n">
-        <v>80182</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541952</v>
+        <v>541941</v>
       </c>
       <c r="R3" t="n">
-        <v>7192657</v>
+        <v>7192545</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129319212</v>
+        <v>129319211</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>80187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541941</v>
+        <v>541952</v>
       </c>
       <c r="R4" t="n">
-        <v>7192545</v>
+        <v>7192657</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,30 +996,34 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319220</v>
+        <v>129319226</v>
       </c>
       <c r="B5" t="n">
-        <v>91608</v>
+        <v>83033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1027,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541916</v>
+        <v>541943</v>
       </c>
       <c r="R5" t="n">
-        <v>7192172</v>
+        <v>7192145</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1062,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1072,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319239</v>
+        <v>129319220</v>
       </c>
       <c r="B6" t="n">
-        <v>80182</v>
+        <v>91613</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,23 +1114,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541707</v>
+        <v>541916</v>
       </c>
       <c r="R6" t="n">
-        <v>7192111</v>
+        <v>7192172</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,32 +1206,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319226</v>
+        <v>129319239</v>
       </c>
       <c r="B7" t="n">
-        <v>83028</v>
+        <v>80187</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541943</v>
+        <v>541707</v>
       </c>
       <c r="R7" t="n">
-        <v>7192145</v>
+        <v>7192111</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,7 +1316,7 @@
         <v>129319222</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129319229</v>
+        <v>129319218</v>
       </c>
       <c r="B9" t="n">
-        <v>91886</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1431,21 +1431,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541938</v>
+        <v>541948</v>
       </c>
       <c r="R9" t="n">
-        <v>7192121</v>
+        <v>7192187</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129319218</v>
+        <v>129319229</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>91891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1538,21 +1538,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541948</v>
+        <v>541938</v>
       </c>
       <c r="R10" t="n">
-        <v>7192187</v>
+        <v>7192121</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1637,7 +1637,7 @@
         <v>129319224</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319240</v>
+        <v>129319215</v>
       </c>
       <c r="B12" t="n">
-        <v>80182</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,21 +1752,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541698</v>
+        <v>541988</v>
       </c>
       <c r="R12" t="n">
-        <v>7192119</v>
+        <v>7192224</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,10 +1848,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129319242</v>
+        <v>129319240</v>
       </c>
       <c r="B13" t="n">
-        <v>57896</v>
+        <v>80187</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,38 +1859,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541676</v>
+        <v>541698</v>
       </c>
       <c r="R13" t="n">
-        <v>7192124</v>
+        <v>7192119</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1922,7 +1918,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1928,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129319215</v>
+        <v>129319242</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>57896</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,34 +1966,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541988</v>
+        <v>541676</v>
       </c>
       <c r="R14" t="n">
-        <v>7192224</v>
+        <v>7192124</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,7 +2069,7 @@
         <v>129319238</v>
       </c>
       <c r="B15" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>129319221</v>
       </c>
       <c r="B16" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>129319237</v>
       </c>
       <c r="B17" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129319219</v>
       </c>
       <c r="B18" t="n">
-        <v>82911</v>
+        <v>82916</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>129319246</v>
       </c>
       <c r="B19" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2601,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129319228</v>
+        <v>129319214</v>
       </c>
       <c r="B20" t="n">
-        <v>91608</v>
+        <v>80186</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2612,19 +2612,23 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2632,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541949</v>
+        <v>541967</v>
       </c>
       <c r="R20" t="n">
-        <v>7192127</v>
+        <v>7192412</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2667,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2677,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,10 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129319214</v>
+        <v>129319228</v>
       </c>
       <c r="B21" t="n">
-        <v>80181</v>
+        <v>91613</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2715,23 +2719,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541967</v>
+        <v>541949</v>
       </c>
       <c r="R21" t="n">
-        <v>7192412</v>
+        <v>7192127</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2814,7 +2814,7 @@
         <v>129319216</v>
       </c>
       <c r="B22" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,32 +2914,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319231</v>
+        <v>129319213</v>
       </c>
       <c r="B23" t="n">
-        <v>79076</v>
+        <v>92548</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541937</v>
+        <v>541932</v>
       </c>
       <c r="R23" t="n">
-        <v>7192124</v>
+        <v>7192500</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3021,32 +3021,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319213</v>
+        <v>129319231</v>
       </c>
       <c r="B24" t="n">
-        <v>92543</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541932</v>
+        <v>541937</v>
       </c>
       <c r="R24" t="n">
-        <v>7192500</v>
+        <v>7192124</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3128,32 +3128,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129319230</v>
+        <v>129319223</v>
       </c>
       <c r="B25" t="n">
-        <v>91588</v>
+        <v>92311</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541937</v>
+        <v>541931</v>
       </c>
       <c r="R25" t="n">
-        <v>7192124</v>
+        <v>7192153</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,10 +3235,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319225</v>
+        <v>129319230</v>
       </c>
       <c r="B26" t="n">
-        <v>82911</v>
+        <v>91593</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3246,21 +3246,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541939</v>
+        <v>541937</v>
       </c>
       <c r="R26" t="n">
-        <v>7192143</v>
+        <v>7192124</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3342,10 +3342,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319244</v>
+        <v>129319225</v>
       </c>
       <c r="B27" t="n">
-        <v>80182</v>
+        <v>82916</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3353,21 +3353,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541664</v>
+        <v>541939</v>
       </c>
       <c r="R27" t="n">
-        <v>7192124</v>
+        <v>7192143</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3449,32 +3449,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319223</v>
+        <v>129319244</v>
       </c>
       <c r="B28" t="n">
-        <v>92306</v>
+        <v>80187</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541931</v>
+        <v>541664</v>
       </c>
       <c r="R28" t="n">
-        <v>7192153</v>
+        <v>7192124</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3559,7 +3559,7 @@
         <v>129319235</v>
       </c>
       <c r="B29" t="n">
-        <v>95995</v>
+        <v>96000</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3663,10 +3663,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319234</v>
+        <v>129319233</v>
       </c>
       <c r="B30" t="n">
-        <v>91588</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3674,21 +3674,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541913</v>
+        <v>541922</v>
       </c>
       <c r="R30" t="n">
-        <v>7192150</v>
+        <v>7192128</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3770,10 +3770,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129319233</v>
+        <v>129319227</v>
       </c>
       <c r="B31" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541922</v>
+        <v>541943</v>
       </c>
       <c r="R31" t="n">
-        <v>7192128</v>
+        <v>7192145</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3877,10 +3877,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129319227</v>
+        <v>129319236</v>
       </c>
       <c r="B32" t="n">
-        <v>79076</v>
+        <v>80187</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,21 +3888,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541943</v>
+        <v>541880</v>
       </c>
       <c r="R32" t="n">
-        <v>7192145</v>
+        <v>7192165</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3984,10 +3984,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129319236</v>
+        <v>129319234</v>
       </c>
       <c r="B33" t="n">
-        <v>80182</v>
+        <v>91593</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3995,21 +3995,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4019,10 +4019,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541880</v>
+        <v>541913</v>
       </c>
       <c r="R33" t="n">
-        <v>7192165</v>
+        <v>7192150</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 44016-2025 artfynd.xlsx
+++ b/artfynd/A 44016-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129319232</v>
+        <v>129319229</v>
       </c>
       <c r="B2" t="n">
-        <v>91891</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541922</v>
+        <v>541938</v>
       </c>
       <c r="R2" t="n">
-        <v>7192133</v>
+        <v>7192121</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129319212</v>
+        <v>129319232</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541941</v>
+        <v>541922</v>
       </c>
       <c r="R3" t="n">
-        <v>7192545</v>
+        <v>7192133</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129319211</v>
+        <v>129319230</v>
       </c>
       <c r="B4" t="n">
-        <v>80187</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541952</v>
+        <v>541937</v>
       </c>
       <c r="R4" t="n">
-        <v>7192657</v>
+        <v>7192124</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129319226</v>
+        <v>129319234</v>
       </c>
       <c r="B5" t="n">
-        <v>83033</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541943</v>
+        <v>541913</v>
       </c>
       <c r="R5" t="n">
-        <v>7192145</v>
+        <v>7192150</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129319220</v>
+        <v>129319219</v>
       </c>
       <c r="B6" t="n">
-        <v>91613</v>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,19 +1114,23 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1134,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541916</v>
+        <v>541925</v>
       </c>
       <c r="R6" t="n">
-        <v>7192172</v>
+        <v>7192171</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1169,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1179,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129319239</v>
+        <v>129319225</v>
       </c>
       <c r="B7" t="n">
-        <v>80187</v>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541707</v>
+        <v>541939</v>
       </c>
       <c r="R7" t="n">
-        <v>7192111</v>
+        <v>7192143</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1276,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1286,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129319222</v>
+        <v>129319211</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1324,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1348,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541917</v>
+        <v>541952</v>
       </c>
       <c r="R8" t="n">
-        <v>7192154</v>
+        <v>7192657</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1383,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1393,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1420,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129319218</v>
+        <v>129319236</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1431,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541948</v>
+        <v>541880</v>
       </c>
       <c r="R9" t="n">
-        <v>7192187</v>
+        <v>7192165</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1490,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1500,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129319229</v>
+        <v>129319239</v>
       </c>
       <c r="B10" t="n">
-        <v>91891</v>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1538,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541938</v>
+        <v>541707</v>
       </c>
       <c r="R10" t="n">
-        <v>7192121</v>
+        <v>7192111</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1597,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1607,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129319224</v>
+        <v>129319240</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541931</v>
+        <v>541698</v>
       </c>
       <c r="R11" t="n">
-        <v>7192150</v>
+        <v>7192119</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1704,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1714,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1741,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129319215</v>
+        <v>129319244</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1752,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1776,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541988</v>
+        <v>541664</v>
       </c>
       <c r="R12" t="n">
-        <v>7192224</v>
+        <v>7192124</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1811,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1821,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,32 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129319240</v>
+        <v>129319235</v>
       </c>
       <c r="B13" t="n">
-        <v>80187</v>
+        <v>96338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541698</v>
+        <v>541915</v>
       </c>
       <c r="R13" t="n">
-        <v>7192119</v>
+        <v>7192139</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1918,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1928,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,49 +1959,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129319242</v>
+        <v>129319223</v>
       </c>
       <c r="B14" t="n">
-        <v>57896</v>
+        <v>92632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541676</v>
+        <v>541931</v>
       </c>
       <c r="R14" t="n">
-        <v>7192124</v>
+        <v>7192153</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,32 +2066,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129319238</v>
+        <v>129319213</v>
       </c>
       <c r="B15" t="n">
-        <v>80186</v>
+        <v>92869</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541732</v>
+        <v>541932</v>
       </c>
       <c r="R15" t="n">
-        <v>7192112</v>
+        <v>7192500</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,32 +2173,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129319221</v>
+        <v>129319212</v>
       </c>
       <c r="B16" t="n">
-        <v>97645</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541917</v>
+        <v>541941</v>
       </c>
       <c r="R16" t="n">
-        <v>7192154</v>
+        <v>7192545</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,14 +2280,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129319237</v>
+        <v>129319215</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541869</v>
+        <v>541988</v>
       </c>
       <c r="R17" t="n">
-        <v>7192158</v>
+        <v>7192224</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,32 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129319219</v>
+        <v>129319218</v>
       </c>
       <c r="B18" t="n">
-        <v>82916</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541925</v>
+        <v>541948</v>
       </c>
       <c r="R18" t="n">
-        <v>7192171</v>
+        <v>7192187</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,14 +2494,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129319246</v>
+        <v>129319222</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541653</v>
+        <v>541917</v>
       </c>
       <c r="R19" t="n">
-        <v>7192124</v>
+        <v>7192154</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,32 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129319214</v>
+        <v>129319224</v>
       </c>
       <c r="B20" t="n">
-        <v>80186</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541967</v>
+        <v>541931</v>
       </c>
       <c r="R20" t="n">
-        <v>7192412</v>
+        <v>7192150</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,30 +2708,34 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129319228</v>
+        <v>129319227</v>
       </c>
       <c r="B21" t="n">
-        <v>91613</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2739,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541949</v>
+        <v>541943</v>
       </c>
       <c r="R21" t="n">
-        <v>7192127</v>
+        <v>7192145</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2774,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2784,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2811,30 +2815,34 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129319216</v>
+        <v>129319231</v>
       </c>
       <c r="B22" t="n">
-        <v>91613</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2842,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541987</v>
+        <v>541937</v>
       </c>
       <c r="R22" t="n">
-        <v>7192223</v>
+        <v>7192124</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2877,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2887,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2914,32 +2922,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129319213</v>
+        <v>129319233</v>
       </c>
       <c r="B23" t="n">
-        <v>92548</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2949,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541932</v>
+        <v>541922</v>
       </c>
       <c r="R23" t="n">
-        <v>7192500</v>
+        <v>7192128</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2984,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2994,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3021,14 +3029,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129319231</v>
+        <v>129319237</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3056,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541937</v>
+        <v>541869</v>
       </c>
       <c r="R24" t="n">
-        <v>7192124</v>
+        <v>7192158</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3091,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3101,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3128,32 +3136,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129319223</v>
+        <v>129319246</v>
       </c>
       <c r="B25" t="n">
-        <v>92311</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3163,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541931</v>
+        <v>541653</v>
       </c>
       <c r="R25" t="n">
-        <v>7192153</v>
+        <v>7192124</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3198,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3208,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3235,32 +3243,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129319230</v>
+        <v>129319226</v>
       </c>
       <c r="B26" t="n">
-        <v>91593</v>
+        <v>83290</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6439</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3270,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541937</v>
+        <v>541943</v>
       </c>
       <c r="R26" t="n">
-        <v>7192124</v>
+        <v>7192145</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3305,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3315,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3342,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129319225</v>
+        <v>129319214</v>
       </c>
       <c r="B27" t="n">
-        <v>82916</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3353,21 +3361,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3377,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541939</v>
+        <v>541967</v>
       </c>
       <c r="R27" t="n">
-        <v>7192143</v>
+        <v>7192412</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3412,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3422,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3449,10 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129319244</v>
+        <v>129319238</v>
       </c>
       <c r="B28" t="n">
-        <v>80187</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3460,21 +3468,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3484,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541664</v>
+        <v>541732</v>
       </c>
       <c r="R28" t="n">
-        <v>7192124</v>
+        <v>7192112</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3519,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3529,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3556,45 +3564,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129319235</v>
+        <v>129319242</v>
       </c>
       <c r="B29" t="n">
-        <v>96000</v>
+        <v>58114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2809</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kroksjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541915</v>
+        <v>541676</v>
       </c>
       <c r="R29" t="n">
-        <v>7192139</v>
+        <v>7192124</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3626,7 +3638,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3636,7 +3648,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3663,32 +3675,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129319233</v>
+        <v>129319221</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>97983</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3698,10 +3710,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541922</v>
+        <v>541917</v>
       </c>
       <c r="R30" t="n">
-        <v>7192128</v>
+        <v>7192154</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3733,7 +3745,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3743,7 +3755,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3767,327 +3779,6 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>129319227</v>
-      </c>
-      <c r="B31" t="n">
-        <v>79081</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Kroksjöberget, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>541943</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7192145</v>
-      </c>
-      <c r="S31" t="n">
-        <v>25</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>129319236</v>
-      </c>
-      <c r="B32" t="n">
-        <v>80187</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Kroksjöberget, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>541880</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7192165</v>
-      </c>
-      <c r="S32" t="n">
-        <v>25</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>129319234</v>
-      </c>
-      <c r="B33" t="n">
-        <v>91593</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Kroksjöberget, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>541913</v>
-      </c>
-      <c r="R33" t="n">
-        <v>7192150</v>
-      </c>
-      <c r="S33" t="n">
-        <v>25</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
